--- a/products/personal-budget-dashboard-rose.xlsx
+++ b/products/personal-budget-dashboard-rose.xlsx
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Bills!$A$1:$E$28</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Budget Setup'!$A$1:$E$37</definedName>
-    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Dashboard!$A$1:$O$33</definedName>
+    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Dashboard!$A$1:$O$39</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Debt Payoff'!$A$1:$G$29</definedName>
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Savings Goals'!$A$1:$G$20</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Start Here'!$A$1:$H$36</definedName>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="146">
   <si>
     <t xml:space="preserve">Personal Budget Dashboard</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t xml:space="preserve">% used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSIGHTS — written automatically from your numbers</t>
   </si>
   <si>
     <t xml:space="preserve">Year Overview</t>
@@ -490,7 +493,7 @@
     <numFmt numFmtId="171" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="172" formatCode="#,##0;\(#,##0\);\-"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -648,6 +651,14 @@
       <b val="true"/>
       <sz val="16"/>
       <color rgb="FF8E4160"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -820,7 +831,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1013,15 +1024,27 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="25" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="26" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1033,7 +1056,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1046,7 +1069,39 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8E4160"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9FAFC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F2937"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -1490,11 +1545,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="8739293"/>
-        <c:axId val="14703285"/>
+        <c:axId val="3381741"/>
+        <c:axId val="60020568"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="8739293"/>
+        <c:axId val="3381741"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1526,7 +1581,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14703285"/>
+        <c:crossAx val="60020568"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1534,7 +1589,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="14703285"/>
+        <c:axId val="60020568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1576,7 +1631,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8739293"/>
+        <c:crossAx val="3381741"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1827,11 +1882,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="33003739"/>
-        <c:axId val="63325394"/>
+        <c:axId val="98163557"/>
+        <c:axId val="86431522"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="33003739"/>
+        <c:axId val="98163557"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1863,7 +1918,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63325394"/>
+        <c:crossAx val="86431522"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1871,7 +1926,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="63325394"/>
+        <c:axId val="86431522"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1913,7 +1968,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33003739"/>
+        <c:crossAx val="98163557"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2006,6 +2061,18 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TxLog" displayName="TxLog" ref="A5:D305" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:D305"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Description"/>
+    <tableColumn id="3" name="Category"/>
+    <tableColumn id="4" name="Amount"/>
+  </tableColumns>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3854,7 +3921,7 @@
       </c>
       <c r="F6" s="23" t="n">
         <f aca="true">IF(ISNUMBER($E6),EDATE(TODAY(),$E6),"")</f>
-        <v>47037</v>
+        <v>47038</v>
       </c>
       <c r="G6" s="24" t="n">
         <f aca="false">IF(ISNUMBER($E6),ROUND($D6*NPER($C6/12,-$D6,$B6)-$B6,2),"")</f>
@@ -3882,7 +3949,7 @@
       </c>
       <c r="F7" s="23" t="n">
         <f aca="true">IF(ISNUMBER($E7),EDATE(TODAY(),$E7),"")</f>
-        <v>46763</v>
+        <v>46764</v>
       </c>
       <c r="G7" s="24" t="n">
         <f aca="false">IF(ISNUMBER($E7),ROUND($D7*NPER($C7/12,-$D7,$B7)-$B7,2),"")</f>
@@ -6196,7 +6263,7 @@
       <c r="D305" s="39"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" autoFilter="false"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -6214,6 +6281,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -7124,12 +7194,14 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="B33" s="49"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -7141,12 +7213,15 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+    <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="50" t="str">
+        <f aca="true">IFERROR(IF($E$7=0,"No spending logged for this month yet.",IF(AND($B$4=MONTH(TODAY()),$D$4=YEAR(TODAY())),"On pace for "&amp;TEXT(ROUND($E$7/DAY(TODAY())*DAY(EOMONTH(TODAY(),0)),0),"$#,##0")&amp;" by month-end — "&amp;IF(ROUND($E$7/DAY(TODAY())*DAY(EOMONTH(TODAY(),0)),0)&lt;=$C$7,"under","over")&amp;" your "&amp;TEXT($C$7,"$#,##0")&amp;" budget.","You spent "&amp;TEXT($E$7,"$#,##0")&amp;" — "&amp;TEXT($E$7/$C$7,"0%")&amp;" of budget.")),"")</f>
+        <v>On pace for $4,607 by month-end — over your $4,455 budget.</v>
+      </c>
+      <c r="B34" s="50"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -7158,12 +7233,15 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
+    <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="50" t="str">
+        <f aca="false">IFERROR(IF(MIN($D$12:$D$31)&lt;0,INDEX($A$12:$A$31,MATCH(MIN($D$12:$D$31),$D$12:$D$31,0))&amp;" is "&amp;TEXT(-MIN($D$12:$D$31),"$#,##0")&amp;" over budget — your biggest overrun.","No category is over budget."),"")</f>
+        <v>No category is over budget.</v>
+      </c>
+      <c r="B35" s="50"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -7175,12 +7253,15 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
+    <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="50" t="str">
+        <f aca="false">IFERROR(IF(MAX($D$12:$D$31)&gt;0,"Most room left: "&amp;INDEX($A$12:$A$31,MATCH(MAX($D$12:$D$31),$D$12:$D$31,0))&amp;" ("&amp;TEXT(MAX($D$12:$D$31),"$#,##0")&amp;" unspent).",""),"")</f>
+        <v>Most room left: Savings &amp; investing ($500 unspent).</v>
+      </c>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -7192,12 +7273,15 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
+    <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="50" t="str">
+        <f aca="false">IFERROR(IF(SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4,1))=0,"Nothing was logged the month before.",IF($E$7&gt;=SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4,1)),"▲ Spending is up ","▼ Spending is down ")&amp;TEXT(ABS($E$7-SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4,1)))/SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4,1)),"0%")&amp;" vs the month before."),"")</f>
+        <v>▼ Spending is down 5% vs the month before.</v>
+      </c>
+      <c r="B37" s="50"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="50"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -7209,12 +7293,15 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
+    <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="50" t="str">
+        <f aca="false">IFERROR(IF($E$7=0,"","Largest single purchase this month: "&amp;TEXT(_xlfn.MAXIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)),"$#,##0")&amp;"."),"")</f>
+        <v>Largest single purchase this month: $1,600.</v>
+      </c>
+      <c r="B38" s="50"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -7347,7 +7434,7 @@
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>
-  <mergeCells count="11">
+  <mergeCells count="16">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="E4:G4"/>
@@ -7359,12 +7446,17 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:G7"/>
     <mergeCell ref="H7:I7"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A38:E38"/>
   </mergeCells>
   <conditionalFormatting sqref="E12:E31">
-    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>0.8</formula>
     </cfRule>
     <cfRule type="dataBar" priority="4">
@@ -7375,7 +7467,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F59959F8-46C4-48EC-91BC-9ADA616CFAAF}</x14:id>
+          <x14:id>{89AFAB4C-2C1F-4586-B865-2488F013F010}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7398,7 +7490,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F59959F8-46C4-48EC-91BC-9ADA616CFAAF}">
+          <x14:cfRule type="dataBar" id="{89AFAB4C-2C1F-4586-B865-2488F013F010}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -7434,7 +7526,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7454,7 +7546,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7532,7 +7624,7 @@
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -7552,13 +7644,13 @@
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>109</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -7576,7 +7668,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="45" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B8" s="46" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,2,1))</f>
@@ -7602,7 +7694,7 @@
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="45" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B9" s="46" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,2,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,3,1))</f>
@@ -7628,7 +7720,7 @@
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="45" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B10" s="46" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,3,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,4,1))</f>
@@ -7654,7 +7746,7 @@
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="45" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B11" s="46" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,5,1))</f>
@@ -7680,7 +7772,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B12" s="46" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,5,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,6,1))</f>
@@ -7706,7 +7798,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="45" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B13" s="46" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,6,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,7,1))</f>
@@ -7732,7 +7824,7 @@
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="45" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B14" s="46" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,7,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,8,1))</f>
@@ -7758,7 +7850,7 @@
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="45" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" s="46" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,8,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,9,1))</f>
@@ -7784,7 +7876,7 @@
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="45" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B16" s="46" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,9,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,10,1))</f>
@@ -7810,7 +7902,7 @@
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="45" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B17" s="46" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,10,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,11,1))</f>
@@ -7836,7 +7928,7 @@
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="45" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B18" s="46" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,11,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,12,1))</f>
@@ -7862,7 +7954,7 @@
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="45" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B19" s="46" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,12,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,13,1))</f>
@@ -7888,9 +7980,9 @@
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="B20" s="48" t="n">
+        <v>130</v>
+      </c>
+      <c r="B20" s="51" t="n">
         <f aca="false">SUM(B8:B19)</f>
         <v>3657</v>
       </c>
@@ -7965,13 +8057,13 @@
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -7990,95 +8082,95 @@
         <v>33</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="49" t="str">
+      <c r="A26" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A15="","",'Budget Setup'!A15)</f>
         <v>Housing</v>
       </c>
-      <c r="B26" s="50" t="n">
+      <c r="B26" s="53" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C26" s="50" t="n">
+      <c r="C26" s="53" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D26" s="50" t="n">
+      <c r="D26" s="53" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E26" s="50" t="n">
+      <c r="E26" s="53" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F26" s="50" t="n">
+      <c r="F26" s="53" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G26" s="50" t="n">
+      <c r="G26" s="53" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H26" s="50" t="n">
+      <c r="H26" s="53" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>1600</v>
       </c>
-      <c r="I26" s="50" t="n">
+      <c r="I26" s="53" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>1600</v>
       </c>
-      <c r="J26" s="50" t="n">
+      <c r="J26" s="53" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K26" s="50" t="n">
+      <c r="K26" s="53" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L26" s="50" t="n">
+      <c r="L26" s="53" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M26" s="50" t="n">
+      <c r="M26" s="53" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8087,55 +8179,55 @@
       <c r="P26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="49" t="str">
+      <c r="A27" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A16="","",'Budget Setup'!A16)</f>
         <v>Groceries</v>
       </c>
-      <c r="B27" s="50" t="n">
+      <c r="B27" s="53" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C27" s="50" t="n">
+      <c r="C27" s="53" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D27" s="50" t="n">
+      <c r="D27" s="53" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E27" s="50" t="n">
+      <c r="E27" s="53" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F27" s="50" t="n">
+      <c r="F27" s="53" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G27" s="50" t="n">
+      <c r="G27" s="53" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H27" s="50" t="n">
+      <c r="H27" s="53" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>184.5</v>
       </c>
-      <c r="I27" s="50" t="n">
+      <c r="I27" s="53" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>84.2</v>
       </c>
-      <c r="J27" s="50" t="n">
+      <c r="J27" s="53" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K27" s="50" t="n">
+      <c r="K27" s="53" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L27" s="50" t="n">
+      <c r="L27" s="53" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M27" s="50" t="n">
+      <c r="M27" s="53" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8144,55 +8236,55 @@
       <c r="P27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="49" t="str">
+      <c r="A28" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A17="","",'Budget Setup'!A17)</f>
         <v>Dining out</v>
       </c>
-      <c r="B28" s="50" t="n">
+      <c r="B28" s="53" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C28" s="50" t="n">
+      <c r="C28" s="53" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D28" s="50" t="n">
+      <c r="D28" s="53" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E28" s="50" t="n">
+      <c r="E28" s="53" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F28" s="50" t="n">
+      <c r="F28" s="53" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G28" s="50" t="n">
+      <c r="G28" s="53" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H28" s="50" t="n">
+      <c r="H28" s="53" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I28" s="50" t="n">
+      <c r="I28" s="53" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>56.8</v>
       </c>
-      <c r="J28" s="50" t="n">
+      <c r="J28" s="53" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K28" s="50" t="n">
+      <c r="K28" s="53" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L28" s="50" t="n">
+      <c r="L28" s="53" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M28" s="50" t="n">
+      <c r="M28" s="53" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8201,55 +8293,55 @@
       <c r="P28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="49" t="str">
+      <c r="A29" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A18="","",'Budget Setup'!A18)</f>
         <v>Transport</v>
       </c>
-      <c r="B29" s="50" t="n">
+      <c r="B29" s="53" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C29" s="50" t="n">
+      <c r="C29" s="53" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D29" s="50" t="n">
+      <c r="D29" s="53" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E29" s="50" t="n">
+      <c r="E29" s="53" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F29" s="50" t="n">
+      <c r="F29" s="53" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G29" s="50" t="n">
+      <c r="G29" s="53" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H29" s="50" t="n">
+      <c r="H29" s="53" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I29" s="50" t="n">
+      <c r="I29" s="53" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>42.5</v>
       </c>
-      <c r="J29" s="50" t="n">
+      <c r="J29" s="53" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K29" s="50" t="n">
+      <c r="K29" s="53" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L29" s="50" t="n">
+      <c r="L29" s="53" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M29" s="50" t="n">
+      <c r="M29" s="53" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8258,55 +8350,55 @@
       <c r="P29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="49" t="str">
+      <c r="A30" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A19="","",'Budget Setup'!A19)</f>
         <v>Utilities</v>
       </c>
-      <c r="B30" s="50" t="n">
+      <c r="B30" s="53" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C30" s="50" t="n">
+      <c r="C30" s="53" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D30" s="50" t="n">
+      <c r="D30" s="53" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E30" s="50" t="n">
+      <c r="E30" s="53" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F30" s="50" t="n">
+      <c r="F30" s="53" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G30" s="50" t="n">
+      <c r="G30" s="53" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H30" s="50" t="n">
+      <c r="H30" s="53" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I30" s="50" t="n">
+      <c r="I30" s="53" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J30" s="50" t="n">
+      <c r="J30" s="53" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K30" s="50" t="n">
+      <c r="K30" s="53" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L30" s="50" t="n">
+      <c r="L30" s="53" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M30" s="50" t="n">
+      <c r="M30" s="53" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8315,55 +8407,55 @@
       <c r="P30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="49" t="str">
+      <c r="A31" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A20="","",'Budget Setup'!A20)</f>
         <v>Phone &amp; internet</v>
       </c>
-      <c r="B31" s="50" t="n">
+      <c r="B31" s="53" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C31" s="50" t="n">
+      <c r="C31" s="53" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D31" s="50" t="n">
+      <c r="D31" s="53" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E31" s="50" t="n">
+      <c r="E31" s="53" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F31" s="50" t="n">
+      <c r="F31" s="53" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G31" s="50" t="n">
+      <c r="G31" s="53" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H31" s="50" t="n">
+      <c r="H31" s="53" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I31" s="50" t="n">
+      <c r="I31" s="53" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J31" s="50" t="n">
+      <c r="J31" s="53" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K31" s="50" t="n">
+      <c r="K31" s="53" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L31" s="50" t="n">
+      <c r="L31" s="53" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M31" s="50" t="n">
+      <c r="M31" s="53" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8372,55 +8464,55 @@
       <c r="P31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="49" t="str">
+      <c r="A32" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A21="","",'Budget Setup'!A21)</f>
         <v>Insurance</v>
       </c>
-      <c r="B32" s="50" t="n">
+      <c r="B32" s="53" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C32" s="50" t="n">
+      <c r="C32" s="53" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D32" s="50" t="n">
+      <c r="D32" s="53" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E32" s="50" t="n">
+      <c r="E32" s="53" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F32" s="50" t="n">
+      <c r="F32" s="53" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G32" s="50" t="n">
+      <c r="G32" s="53" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H32" s="50" t="n">
+      <c r="H32" s="53" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I32" s="50" t="n">
+      <c r="I32" s="53" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J32" s="50" t="n">
+      <c r="J32" s="53" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K32" s="50" t="n">
+      <c r="K32" s="53" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L32" s="50" t="n">
+      <c r="L32" s="53" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M32" s="50" t="n">
+      <c r="M32" s="53" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8429,55 +8521,55 @@
       <c r="P32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="str">
+      <c r="A33" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A22="","",'Budget Setup'!A22)</f>
         <v>Health &amp; fitness</v>
       </c>
-      <c r="B33" s="50" t="n">
+      <c r="B33" s="53" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C33" s="50" t="n">
+      <c r="C33" s="53" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D33" s="50" t="n">
+      <c r="D33" s="53" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E33" s="50" t="n">
+      <c r="E33" s="53" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F33" s="50" t="n">
+      <c r="F33" s="53" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G33" s="50" t="n">
+      <c r="G33" s="53" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H33" s="50" t="n">
+      <c r="H33" s="53" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I33" s="50" t="n">
+      <c r="I33" s="53" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J33" s="50" t="n">
+      <c r="J33" s="53" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K33" s="50" t="n">
+      <c r="K33" s="53" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L33" s="50" t="n">
+      <c r="L33" s="53" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M33" s="50" t="n">
+      <c r="M33" s="53" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8486,55 +8578,55 @@
       <c r="P33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49" t="str">
+      <c r="A34" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A23="","",'Budget Setup'!A23)</f>
         <v>Entertainment</v>
       </c>
-      <c r="B34" s="50" t="n">
+      <c r="B34" s="53" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C34" s="50" t="n">
+      <c r="C34" s="53" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D34" s="50" t="n">
+      <c r="D34" s="53" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E34" s="50" t="n">
+      <c r="E34" s="53" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F34" s="50" t="n">
+      <c r="F34" s="53" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G34" s="50" t="n">
+      <c r="G34" s="53" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H34" s="50" t="n">
+      <c r="H34" s="53" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>89</v>
       </c>
-      <c r="I34" s="50" t="n">
+      <c r="I34" s="53" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J34" s="50" t="n">
+      <c r="J34" s="53" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K34" s="50" t="n">
+      <c r="K34" s="53" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L34" s="50" t="n">
+      <c r="L34" s="53" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M34" s="50" t="n">
+      <c r="M34" s="53" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8543,55 +8635,55 @@
       <c r="P34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="49" t="str">
+      <c r="A35" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A24="","",'Budget Setup'!A24)</f>
         <v>Subscriptions</v>
       </c>
-      <c r="B35" s="50" t="n">
+      <c r="B35" s="53" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C35" s="50" t="n">
+      <c r="C35" s="53" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D35" s="50" t="n">
+      <c r="D35" s="53" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E35" s="50" t="n">
+      <c r="E35" s="53" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F35" s="50" t="n">
+      <c r="F35" s="53" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G35" s="50" t="n">
+      <c r="G35" s="53" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H35" s="50" t="n">
+      <c r="H35" s="53" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I35" s="50" t="n">
+      <c r="I35" s="53" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J35" s="50" t="n">
+      <c r="J35" s="53" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K35" s="50" t="n">
+      <c r="K35" s="53" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L35" s="50" t="n">
+      <c r="L35" s="53" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M35" s="50" t="n">
+      <c r="M35" s="53" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8600,55 +8692,55 @@
       <c r="P35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="49" t="str">
+      <c r="A36" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A25="","",'Budget Setup'!A25)</f>
         <v>Shopping</v>
       </c>
-      <c r="B36" s="50" t="n">
+      <c r="B36" s="53" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C36" s="50" t="n">
+      <c r="C36" s="53" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D36" s="50" t="n">
+      <c r="D36" s="53" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E36" s="50" t="n">
+      <c r="E36" s="53" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F36" s="50" t="n">
+      <c r="F36" s="53" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G36" s="50" t="n">
+      <c r="G36" s="53" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H36" s="50" t="n">
+      <c r="H36" s="53" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I36" s="50" t="n">
+      <c r="I36" s="53" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J36" s="50" t="n">
+      <c r="J36" s="53" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K36" s="50" t="n">
+      <c r="K36" s="53" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L36" s="50" t="n">
+      <c r="L36" s="53" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M36" s="50" t="n">
+      <c r="M36" s="53" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8657,55 +8749,55 @@
       <c r="P36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="49" t="str">
+      <c r="A37" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A26="","",'Budget Setup'!A26)</f>
         <v>Personal care</v>
       </c>
-      <c r="B37" s="50" t="n">
+      <c r="B37" s="53" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C37" s="50" t="n">
+      <c r="C37" s="53" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D37" s="50" t="n">
+      <c r="D37" s="53" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E37" s="50" t="n">
+      <c r="E37" s="53" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F37" s="50" t="n">
+      <c r="F37" s="53" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G37" s="50" t="n">
+      <c r="G37" s="53" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H37" s="50" t="n">
+      <c r="H37" s="53" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I37" s="50" t="n">
+      <c r="I37" s="53" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J37" s="50" t="n">
+      <c r="J37" s="53" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K37" s="50" t="n">
+      <c r="K37" s="53" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L37" s="50" t="n">
+      <c r="L37" s="53" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M37" s="50" t="n">
+      <c r="M37" s="53" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8714,55 +8806,55 @@
       <c r="P37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="49" t="str">
+      <c r="A38" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A27="","",'Budget Setup'!A27)</f>
         <v>Savings &amp; investing</v>
       </c>
-      <c r="B38" s="50" t="n">
+      <c r="B38" s="53" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C38" s="50" t="n">
+      <c r="C38" s="53" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D38" s="50" t="n">
+      <c r="D38" s="53" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E38" s="50" t="n">
+      <c r="E38" s="53" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F38" s="50" t="n">
+      <c r="F38" s="53" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G38" s="50" t="n">
+      <c r="G38" s="53" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H38" s="50" t="n">
+      <c r="H38" s="53" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I38" s="50" t="n">
+      <c r="I38" s="53" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J38" s="50" t="n">
+      <c r="J38" s="53" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K38" s="50" t="n">
+      <c r="K38" s="53" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L38" s="50" t="n">
+      <c r="L38" s="53" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M38" s="50" t="n">
+      <c r="M38" s="53" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8771,55 +8863,55 @@
       <c r="P38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="49" t="str">
+      <c r="A39" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A28="","",'Budget Setup'!A28)</f>
         <v>Debt payments</v>
       </c>
-      <c r="B39" s="50" t="n">
+      <c r="B39" s="53" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C39" s="50" t="n">
+      <c r="C39" s="53" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D39" s="50" t="n">
+      <c r="D39" s="53" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E39" s="50" t="n">
+      <c r="E39" s="53" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F39" s="50" t="n">
+      <c r="F39" s="53" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G39" s="50" t="n">
+      <c r="G39" s="53" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H39" s="50" t="n">
+      <c r="H39" s="53" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I39" s="50" t="n">
+      <c r="I39" s="53" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J39" s="50" t="n">
+      <c r="J39" s="53" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K39" s="50" t="n">
+      <c r="K39" s="53" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L39" s="50" t="n">
+      <c r="L39" s="53" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M39" s="50" t="n">
+      <c r="M39" s="53" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8828,55 +8920,55 @@
       <c r="P39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="49" t="str">
+      <c r="A40" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A29="","",'Budget Setup'!A29)</f>
         <v>Everything else</v>
       </c>
-      <c r="B40" s="50" t="n">
+      <c r="B40" s="53" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C40" s="50" t="n">
+      <c r="C40" s="53" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D40" s="50" t="n">
+      <c r="D40" s="53" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E40" s="50" t="n">
+      <c r="E40" s="53" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F40" s="50" t="n">
+      <c r="F40" s="53" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G40" s="50" t="n">
+      <c r="G40" s="53" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H40" s="50" t="n">
+      <c r="H40" s="53" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I40" s="50" t="n">
+      <c r="I40" s="53" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J40" s="50" t="n">
+      <c r="J40" s="53" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K40" s="50" t="n">
+      <c r="K40" s="53" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L40" s="50" t="n">
+      <c r="L40" s="53" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M40" s="50" t="n">
+      <c r="M40" s="53" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8885,55 +8977,55 @@
       <c r="P40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="49" t="str">
+      <c r="A41" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A30="","",'Budget Setup'!A30)</f>
         <v/>
       </c>
-      <c r="B41" s="50" t="str">
+      <c r="B41" s="53" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="C41" s="50" t="str">
+      <c r="C41" s="53" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="D41" s="50" t="str">
+      <c r="D41" s="53" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="E41" s="50" t="str">
+      <c r="E41" s="53" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="F41" s="50" t="str">
+      <c r="F41" s="53" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="G41" s="50" t="str">
+      <c r="G41" s="53" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="H41" s="50" t="str">
+      <c r="H41" s="53" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="I41" s="50" t="str">
+      <c r="I41" s="53" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="J41" s="50" t="str">
+      <c r="J41" s="53" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="K41" s="50" t="str">
+      <c r="K41" s="53" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="L41" s="50" t="str">
+      <c r="L41" s="53" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="M41" s="50" t="str">
+      <c r="M41" s="53" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
@@ -8942,55 +9034,55 @@
       <c r="P41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="49" t="str">
+      <c r="A42" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A31="","",'Budget Setup'!A31)</f>
         <v/>
       </c>
-      <c r="B42" s="50" t="str">
+      <c r="B42" s="53" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="C42" s="50" t="str">
+      <c r="C42" s="53" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="D42" s="50" t="str">
+      <c r="D42" s="53" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="E42" s="50" t="str">
+      <c r="E42" s="53" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="F42" s="50" t="str">
+      <c r="F42" s="53" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="G42" s="50" t="str">
+      <c r="G42" s="53" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="H42" s="50" t="str">
+      <c r="H42" s="53" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="I42" s="50" t="str">
+      <c r="I42" s="53" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="J42" s="50" t="str">
+      <c r="J42" s="53" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="K42" s="50" t="str">
+      <c r="K42" s="53" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="L42" s="50" t="str">
+      <c r="L42" s="53" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="M42" s="50" t="str">
+      <c r="M42" s="53" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
@@ -8999,55 +9091,55 @@
       <c r="P42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="49" t="str">
+      <c r="A43" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A32="","",'Budget Setup'!A32)</f>
         <v/>
       </c>
-      <c r="B43" s="50" t="str">
+      <c r="B43" s="53" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="C43" s="50" t="str">
+      <c r="C43" s="53" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="D43" s="50" t="str">
+      <c r="D43" s="53" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="E43" s="50" t="str">
+      <c r="E43" s="53" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="F43" s="50" t="str">
+      <c r="F43" s="53" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="G43" s="50" t="str">
+      <c r="G43" s="53" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="H43" s="50" t="str">
+      <c r="H43" s="53" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="I43" s="50" t="str">
+      <c r="I43" s="53" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="J43" s="50" t="str">
+      <c r="J43" s="53" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="K43" s="50" t="str">
+      <c r="K43" s="53" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="L43" s="50" t="str">
+      <c r="L43" s="53" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="M43" s="50" t="str">
+      <c r="M43" s="53" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
@@ -9056,55 +9148,55 @@
       <c r="P43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="49" t="str">
+      <c r="A44" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A33="","",'Budget Setup'!A33)</f>
         <v/>
       </c>
-      <c r="B44" s="50" t="str">
+      <c r="B44" s="53" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="C44" s="50" t="str">
+      <c r="C44" s="53" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="D44" s="50" t="str">
+      <c r="D44" s="53" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="E44" s="50" t="str">
+      <c r="E44" s="53" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="F44" s="50" t="str">
+      <c r="F44" s="53" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="G44" s="50" t="str">
+      <c r="G44" s="53" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="H44" s="50" t="str">
+      <c r="H44" s="53" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="I44" s="50" t="str">
+      <c r="I44" s="53" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="J44" s="50" t="str">
+      <c r="J44" s="53" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="K44" s="50" t="str">
+      <c r="K44" s="53" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="L44" s="50" t="str">
+      <c r="L44" s="53" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="M44" s="50" t="str">
+      <c r="M44" s="53" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
@@ -9113,55 +9205,55 @@
       <c r="P44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="49" t="str">
+      <c r="A45" s="52" t="str">
         <f aca="false">IF('Budget Setup'!A34="","",'Budget Setup'!A34)</f>
         <v/>
       </c>
-      <c r="B45" s="50" t="str">
+      <c r="B45" s="53" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="C45" s="50" t="str">
+      <c r="C45" s="53" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="D45" s="50" t="str">
+      <c r="D45" s="53" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="E45" s="50" t="str">
+      <c r="E45" s="53" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="F45" s="50" t="str">
+      <c r="F45" s="53" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="G45" s="50" t="str">
+      <c r="G45" s="53" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="H45" s="50" t="str">
+      <c r="H45" s="53" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="I45" s="50" t="str">
+      <c r="I45" s="53" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="J45" s="50" t="str">
+      <c r="J45" s="53" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="K45" s="50" t="str">
+      <c r="K45" s="53" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="L45" s="50" t="str">
+      <c r="L45" s="53" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="M45" s="50" t="str">
+      <c r="M45" s="53" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
@@ -9270,7 +9362,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9283,7 +9375,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9307,7 +9399,7 @@
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -9320,32 +9412,32 @@
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B6" s="14" t="n">
         <v>3000</v>
@@ -9353,14 +9445,14 @@
       <c r="C6" s="14" t="n">
         <v>1150</v>
       </c>
-      <c r="D6" s="51" t="n">
+      <c r="D6" s="54" t="n">
         <v>46387</v>
       </c>
-      <c r="E6" s="52" t="n">
+      <c r="E6" s="55" t="n">
         <f aca="true">IF(OR($A6="",$D6=""),"",MAX(0,(YEAR($D6)-YEAR(TODAY()))*12+MONTH($D6)-MONTH(TODAY())))</f>
         <v>4</v>
       </c>
-      <c r="F6" s="53" t="n">
+      <c r="F6" s="56" t="n">
         <f aca="false">IF(OR($A6="",$B6="",$D6=""),"",IF($E6=0,MAX(0,$B6-$C6),ROUND(MAX(0,$B6-$C6)/$E6,2)))</f>
         <v>462.5</v>
       </c>
@@ -9373,7 +9465,7 @@
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B7" s="14" t="n">
         <v>2400</v>
@@ -9381,14 +9473,14 @@
       <c r="C7" s="14" t="n">
         <v>600</v>
       </c>
-      <c r="D7" s="51" t="n">
+      <c r="D7" s="54" t="n">
         <v>46568</v>
       </c>
-      <c r="E7" s="52" t="n">
+      <c r="E7" s="55" t="n">
         <f aca="true">IF(OR($A7="",$D7=""),"",MAX(0,(YEAR($D7)-YEAR(TODAY()))*12+MONTH($D7)-MONTH(TODAY())))</f>
         <v>10</v>
       </c>
-      <c r="F7" s="53" t="n">
+      <c r="F7" s="56" t="n">
         <f aca="false">IF(OR($A7="",$B7="",$D7=""),"",IF($E7=0,MAX(0,$B7-$C7),ROUND(MAX(0,$B7-$C7)/$E7,2)))</f>
         <v>180</v>
       </c>
@@ -9403,12 +9495,12 @@
       <c r="A8" s="13"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="52" t="str">
+      <c r="D8" s="54"/>
+      <c r="E8" s="55" t="str">
         <f aca="true">IF(OR($A8="",$D8=""),"",MAX(0,(YEAR($D8)-YEAR(TODAY()))*12+MONTH($D8)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F8" s="53" t="str">
+      <c r="F8" s="56" t="str">
         <f aca="false">IF(OR($A8="",$B8="",$D8=""),"",IF($E8=0,MAX(0,$B8-$C8),ROUND(MAX(0,$B8-$C8)/$E8,2)))</f>
         <v/>
       </c>
@@ -9423,12 +9515,12 @@
       <c r="A9" s="13"/>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="52" t="str">
+      <c r="D9" s="54"/>
+      <c r="E9" s="55" t="str">
         <f aca="true">IF(OR($A9="",$D9=""),"",MAX(0,(YEAR($D9)-YEAR(TODAY()))*12+MONTH($D9)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F9" s="53" t="str">
+      <c r="F9" s="56" t="str">
         <f aca="false">IF(OR($A9="",$B9="",$D9=""),"",IF($E9=0,MAX(0,$B9-$C9),ROUND(MAX(0,$B9-$C9)/$E9,2)))</f>
         <v/>
       </c>
@@ -9443,12 +9535,12 @@
       <c r="A10" s="13"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="52" t="str">
+      <c r="D10" s="54"/>
+      <c r="E10" s="55" t="str">
         <f aca="true">IF(OR($A10="",$D10=""),"",MAX(0,(YEAR($D10)-YEAR(TODAY()))*12+MONTH($D10)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F10" s="53" t="str">
+      <c r="F10" s="56" t="str">
         <f aca="false">IF(OR($A10="",$B10="",$D10=""),"",IF($E10=0,MAX(0,$B10-$C10),ROUND(MAX(0,$B10-$C10)/$E10,2)))</f>
         <v/>
       </c>
@@ -9463,12 +9555,12 @@
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="52" t="str">
+      <c r="D11" s="54"/>
+      <c r="E11" s="55" t="str">
         <f aca="true">IF(OR($A11="",$D11=""),"",MAX(0,(YEAR($D11)-YEAR(TODAY()))*12+MONTH($D11)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F11" s="53" t="str">
+      <c r="F11" s="56" t="str">
         <f aca="false">IF(OR($A11="",$B11="",$D11=""),"",IF($E11=0,MAX(0,$B11-$C11),ROUND(MAX(0,$B11-$C11)/$E11,2)))</f>
         <v/>
       </c>
@@ -9483,12 +9575,12 @@
       <c r="A12" s="13"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="52" t="str">
+      <c r="D12" s="54"/>
+      <c r="E12" s="55" t="str">
         <f aca="true">IF(OR($A12="",$D12=""),"",MAX(0,(YEAR($D12)-YEAR(TODAY()))*12+MONTH($D12)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F12" s="53" t="str">
+      <c r="F12" s="56" t="str">
         <f aca="false">IF(OR($A12="",$B12="",$D12=""),"",IF($E12=0,MAX(0,$B12-$C12),ROUND(MAX(0,$B12-$C12)/$E12,2)))</f>
         <v/>
       </c>
@@ -9503,12 +9595,12 @@
       <c r="A13" s="13"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="52" t="str">
+      <c r="D13" s="54"/>
+      <c r="E13" s="55" t="str">
         <f aca="true">IF(OR($A13="",$D13=""),"",MAX(0,(YEAR($D13)-YEAR(TODAY()))*12+MONTH($D13)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F13" s="53" t="str">
+      <c r="F13" s="56" t="str">
         <f aca="false">IF(OR($A13="",$B13="",$D13=""),"",IF($E13=0,MAX(0,$B13-$C13),ROUND(MAX(0,$B13-$C13)/$E13,2)))</f>
         <v/>
       </c>
@@ -9523,12 +9615,12 @@
       <c r="A14" s="13"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="52" t="str">
+      <c r="D14" s="54"/>
+      <c r="E14" s="55" t="str">
         <f aca="true">IF(OR($A14="",$D14=""),"",MAX(0,(YEAR($D14)-YEAR(TODAY()))*12+MONTH($D14)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F14" s="53" t="str">
+      <c r="F14" s="56" t="str">
         <f aca="false">IF(OR($A14="",$B14="",$D14=""),"",IF($E14=0,MAX(0,$B14-$C14),ROUND(MAX(0,$B14-$C14)/$E14,2)))</f>
         <v/>
       </c>
@@ -9543,12 +9635,12 @@
       <c r="A15" s="13"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="52" t="str">
+      <c r="D15" s="54"/>
+      <c r="E15" s="55" t="str">
         <f aca="true">IF(OR($A15="",$D15=""),"",MAX(0,(YEAR($D15)-YEAR(TODAY()))*12+MONTH($D15)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F15" s="53" t="str">
+      <c r="F15" s="56" t="str">
         <f aca="false">IF(OR($A15="",$B15="",$D15=""),"",IF($E15=0,MAX(0,$B15-$C15),ROUND(MAX(0,$B15-$C15)/$E15,2)))</f>
         <v/>
       </c>
@@ -9602,7 +9694,7 @@
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -9661,7 +9753,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7AB835E6-2E6E-4C6F-AD24-7AF6CCF0B272}</x14:id>
+          <x14:id>{F3714075-C9CA-4A22-8196-3EED44736965}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -9677,7 +9769,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7AB835E6-2E6E-4C6F-AD24-7AF6CCF0B272}">
+          <x14:cfRule type="dataBar" id="{F3714075-C9CA-4A22-8196-3EED44736965}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/products/personal-budget-dashboard-rose.xlsx
+++ b/products/personal-budget-dashboard-rose.xlsx
@@ -579,8 +579,8 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+      <color rgb="FF8E4160"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -633,7 +633,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="16"/>
+      <sz val="18"/>
       <color rgb="FF1F2937"/>
       <name val="Calibri"/>
       <family val="0"/>
@@ -641,7 +641,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="16"/>
+      <sz val="18"/>
       <color rgb="FFC46E8D"/>
       <name val="Calibri"/>
       <family val="0"/>
@@ -649,7 +649,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="16"/>
+      <sz val="18"/>
       <color rgb="FF8E4160"/>
       <name val="Calibri"/>
       <family val="0"/>
@@ -743,7 +743,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -752,17 +752,20 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFD8DEE9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD8DEE9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD8DEE9"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="FFD8DEE9"/>
+        <color rgb="FFE7EBEE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF8E4160"/>
       </bottom>
       <diagonal/>
     </border>
@@ -776,30 +779,18 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFE3E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE3E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFE3E8F0"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFE3E8F0"/>
       </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFEDF0F4"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFEDF0F4"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFEDF0F4"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFEDF0F4"/>
       </bottom>
@@ -831,7 +822,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -880,7 +871,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -900,7 +891,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -912,7 +903,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -932,7 +923,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -968,6 +959,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="170" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
@@ -996,19 +991,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1032,11 +1027,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1044,7 +1039,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="26" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="26" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1069,15 +1064,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF8E4160"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1097,7 +1084,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF1F2937"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8E4160"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1148,7 +1150,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFC46E8D"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD8DEE9"/>
+      <rgbColor rgb="FFE3E8F0"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1158,7 +1160,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFE3E8F0"/>
+      <rgbColor rgb="FFE7EBEE"/>
       <rgbColor rgb="FFE4E9E6"/>
       <rgbColor rgb="FFFBF6F8"/>
       <rgbColor rgb="FFF9FAFC"/>
@@ -1545,11 +1547,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="3381741"/>
-        <c:axId val="60020568"/>
+        <c:axId val="6831416"/>
+        <c:axId val="72371838"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="3381741"/>
+        <c:axId val="6831416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1581,7 +1583,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60020568"/>
+        <c:crossAx val="72371838"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1589,7 +1591,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60020568"/>
+        <c:axId val="72371838"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1631,7 +1633,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3381741"/>
+        <c:crossAx val="6831416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1882,11 +1884,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="98163557"/>
-        <c:axId val="86431522"/>
+        <c:axId val="31332329"/>
+        <c:axId val="55682244"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="98163557"/>
+        <c:axId val="31332329"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1918,7 +1920,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86431522"/>
+        <c:crossAx val="55682244"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1926,7 +1928,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86431522"/>
+        <c:axId val="55682244"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1968,7 +1970,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98163557"/>
+        <c:crossAx val="31332329"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2006,7 +2008,7 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>285480</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>60840</xdr:rowOff>
+      <xdr:rowOff>32400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2014,7 +2016,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5356800" y="2333520"/>
+        <a:off x="5356800" y="2409840"/>
         <a:ext cx="5219640" cy="4499640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2041,7 +2043,7 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>579960</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>123840</xdr:rowOff>
+      <xdr:rowOff>95040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2896,7 +2898,7 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
         <v>27</v>
       </c>
@@ -3008,7 +3010,7 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
         <v>33</v>
       </c>
@@ -3477,7 +3479,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
         <v>54</v>
       </c>
@@ -3877,7 +3879,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
         <v>71</v>
       </c>
@@ -4384,1883 +4386,1883 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="34" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="34" t="n">
+      <c r="A6" s="35" t="n">
         <v>46204</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="36" t="n">
+      <c r="D6" s="37" t="n">
         <v>1600</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="n">
+      <c r="A7" s="38" t="n">
         <v>46209</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="40" t="n">
         <v>96.4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="34" t="n">
+      <c r="A8" s="35" t="n">
         <v>46221</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="36" t="n">
+      <c r="D8" s="37" t="n">
         <v>89</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="n">
+      <c r="A9" s="38" t="n">
         <v>46227</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="39" t="n">
+      <c r="D9" s="40" t="n">
         <v>88.1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="34" t="n">
+      <c r="A10" s="35" t="n">
         <v>46235</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="36" t="n">
+      <c r="D10" s="37" t="n">
         <v>1600</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="n">
+      <c r="A11" s="38" t="n">
         <v>46237</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D11" s="40" t="n">
         <v>84.2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="34" t="n">
+      <c r="A12" s="35" t="n">
         <v>46239</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="36" t="n">
+      <c r="D12" s="37" t="n">
         <v>42.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="n">
+      <c r="A13" s="38" t="n">
         <v>46242</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="39" t="n">
+      <c r="D13" s="40" t="n">
         <v>56.8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="34"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="36"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="37"/>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="39"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="40"/>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="36"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="37"/>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="37"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="39"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="40"/>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="34"/>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="36"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="37"/>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="37"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="39"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="40"/>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="34"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="36"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="37"/>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="37"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="39"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="40"/>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="36"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="37"/>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="37"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="39"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="40"/>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="34"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="36"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="37"/>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="37"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="39"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="40"/>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="34"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="36"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="37"/>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="37"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="38"/>
-      <c r="D27" s="39"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="40"/>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34"/>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="36"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="37"/>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="37"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="39"/>
+      <c r="A29" s="38"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="40"/>
     </row>
     <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="34"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="36"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="37"/>
     </row>
     <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="37"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="38"/>
-      <c r="D31" s="39"/>
+      <c r="A31" s="38"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="40"/>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="34"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="36"/>
+      <c r="A32" s="35"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="37"/>
     </row>
     <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="37"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="38"/>
-      <c r="D33" s="39"/>
+      <c r="A33" s="38"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="40"/>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="34"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="36"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="37"/>
     </row>
     <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="39"/>
+      <c r="A35" s="38"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="40"/>
     </row>
     <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="34"/>
-      <c r="B36" s="35"/>
-      <c r="C36" s="35"/>
-      <c r="D36" s="36"/>
+      <c r="A36" s="35"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="37"/>
     </row>
     <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="37"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="39"/>
+      <c r="A37" s="38"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="40"/>
     </row>
     <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="34"/>
-      <c r="B38" s="35"/>
-      <c r="C38" s="35"/>
-      <c r="D38" s="36"/>
+      <c r="A38" s="35"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="37"/>
     </row>
     <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="37"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="39"/>
+      <c r="A39" s="38"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="40"/>
     </row>
     <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="34"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="36"/>
+      <c r="A40" s="35"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="37"/>
     </row>
     <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="37"/>
-      <c r="B41" s="38"/>
-      <c r="C41" s="38"/>
-      <c r="D41" s="39"/>
+      <c r="A41" s="38"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="40"/>
     </row>
     <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="34"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="36"/>
+      <c r="A42" s="35"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="37"/>
     </row>
     <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="37"/>
-      <c r="B43" s="38"/>
-      <c r="C43" s="38"/>
-      <c r="D43" s="39"/>
+      <c r="A43" s="38"/>
+      <c r="B43" s="39"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="40"/>
     </row>
     <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="34"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="36"/>
+      <c r="A44" s="35"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="37"/>
     </row>
     <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="37"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="38"/>
-      <c r="D45" s="39"/>
+      <c r="A45" s="38"/>
+      <c r="B45" s="39"/>
+      <c r="C45" s="39"/>
+      <c r="D45" s="40"/>
     </row>
     <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="34"/>
-      <c r="B46" s="35"/>
-      <c r="C46" s="35"/>
-      <c r="D46" s="36"/>
+      <c r="A46" s="35"/>
+      <c r="B46" s="36"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="37"/>
     </row>
     <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="37"/>
-      <c r="B47" s="38"/>
-      <c r="C47" s="38"/>
-      <c r="D47" s="39"/>
+      <c r="A47" s="38"/>
+      <c r="B47" s="39"/>
+      <c r="C47" s="39"/>
+      <c r="D47" s="40"/>
     </row>
     <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="34"/>
-      <c r="B48" s="35"/>
-      <c r="C48" s="35"/>
-      <c r="D48" s="36"/>
+      <c r="A48" s="35"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="36"/>
+      <c r="D48" s="37"/>
     </row>
     <row r="49" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="37"/>
-      <c r="B49" s="38"/>
-      <c r="C49" s="38"/>
-      <c r="D49" s="39"/>
+      <c r="A49" s="38"/>
+      <c r="B49" s="39"/>
+      <c r="C49" s="39"/>
+      <c r="D49" s="40"/>
     </row>
     <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="34"/>
-      <c r="B50" s="35"/>
-      <c r="C50" s="35"/>
-      <c r="D50" s="36"/>
+      <c r="A50" s="35"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="37"/>
     </row>
     <row r="51" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="37"/>
-      <c r="B51" s="38"/>
-      <c r="C51" s="38"/>
-      <c r="D51" s="39"/>
+      <c r="A51" s="38"/>
+      <c r="B51" s="39"/>
+      <c r="C51" s="39"/>
+      <c r="D51" s="40"/>
     </row>
     <row r="52" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="34"/>
-      <c r="B52" s="35"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="36"/>
+      <c r="A52" s="35"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="37"/>
     </row>
     <row r="53" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="37"/>
-      <c r="B53" s="38"/>
-      <c r="C53" s="38"/>
-      <c r="D53" s="39"/>
+      <c r="A53" s="38"/>
+      <c r="B53" s="39"/>
+      <c r="C53" s="39"/>
+      <c r="D53" s="40"/>
     </row>
     <row r="54" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="34"/>
-      <c r="B54" s="35"/>
-      <c r="C54" s="35"/>
-      <c r="D54" s="36"/>
+      <c r="A54" s="35"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="37"/>
     </row>
     <row r="55" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="37"/>
-      <c r="B55" s="38"/>
-      <c r="C55" s="38"/>
-      <c r="D55" s="39"/>
+      <c r="A55" s="38"/>
+      <c r="B55" s="39"/>
+      <c r="C55" s="39"/>
+      <c r="D55" s="40"/>
     </row>
     <row r="56" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="34"/>
-      <c r="B56" s="35"/>
-      <c r="C56" s="35"/>
-      <c r="D56" s="36"/>
+      <c r="A56" s="35"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="36"/>
+      <c r="D56" s="37"/>
     </row>
     <row r="57" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="37"/>
-      <c r="B57" s="38"/>
-      <c r="C57" s="38"/>
-      <c r="D57" s="39"/>
+      <c r="A57" s="38"/>
+      <c r="B57" s="39"/>
+      <c r="C57" s="39"/>
+      <c r="D57" s="40"/>
     </row>
     <row r="58" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="34"/>
-      <c r="B58" s="35"/>
-      <c r="C58" s="35"/>
-      <c r="D58" s="36"/>
+      <c r="A58" s="35"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="36"/>
+      <c r="D58" s="37"/>
     </row>
     <row r="59" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="37"/>
-      <c r="B59" s="38"/>
-      <c r="C59" s="38"/>
-      <c r="D59" s="39"/>
+      <c r="A59" s="38"/>
+      <c r="B59" s="39"/>
+      <c r="C59" s="39"/>
+      <c r="D59" s="40"/>
     </row>
     <row r="60" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="34"/>
-      <c r="B60" s="35"/>
-      <c r="C60" s="35"/>
-      <c r="D60" s="36"/>
+      <c r="A60" s="35"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="36"/>
+      <c r="D60" s="37"/>
     </row>
     <row r="61" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="37"/>
-      <c r="B61" s="38"/>
-      <c r="C61" s="38"/>
-      <c r="D61" s="39"/>
+      <c r="A61" s="38"/>
+      <c r="B61" s="39"/>
+      <c r="C61" s="39"/>
+      <c r="D61" s="40"/>
     </row>
     <row r="62" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="34"/>
-      <c r="B62" s="35"/>
-      <c r="C62" s="35"/>
-      <c r="D62" s="36"/>
+      <c r="A62" s="35"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="37"/>
     </row>
     <row r="63" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="37"/>
-      <c r="B63" s="38"/>
-      <c r="C63" s="38"/>
-      <c r="D63" s="39"/>
+      <c r="A63" s="38"/>
+      <c r="B63" s="39"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="40"/>
     </row>
     <row r="64" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="34"/>
-      <c r="B64" s="35"/>
-      <c r="C64" s="35"/>
-      <c r="D64" s="36"/>
+      <c r="A64" s="35"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="37"/>
     </row>
     <row r="65" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="37"/>
-      <c r="B65" s="38"/>
-      <c r="C65" s="38"/>
-      <c r="D65" s="39"/>
+      <c r="A65" s="38"/>
+      <c r="B65" s="39"/>
+      <c r="C65" s="39"/>
+      <c r="D65" s="40"/>
     </row>
     <row r="66" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="34"/>
-      <c r="B66" s="35"/>
-      <c r="C66" s="35"/>
-      <c r="D66" s="36"/>
+      <c r="A66" s="35"/>
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="37"/>
     </row>
     <row r="67" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="37"/>
-      <c r="B67" s="38"/>
-      <c r="C67" s="38"/>
-      <c r="D67" s="39"/>
+      <c r="A67" s="38"/>
+      <c r="B67" s="39"/>
+      <c r="C67" s="39"/>
+      <c r="D67" s="40"/>
     </row>
     <row r="68" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="34"/>
-      <c r="B68" s="35"/>
-      <c r="C68" s="35"/>
-      <c r="D68" s="36"/>
+      <c r="A68" s="35"/>
+      <c r="B68" s="36"/>
+      <c r="C68" s="36"/>
+      <c r="D68" s="37"/>
     </row>
     <row r="69" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="37"/>
-      <c r="B69" s="38"/>
-      <c r="C69" s="38"/>
-      <c r="D69" s="39"/>
+      <c r="A69" s="38"/>
+      <c r="B69" s="39"/>
+      <c r="C69" s="39"/>
+      <c r="D69" s="40"/>
     </row>
     <row r="70" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="34"/>
-      <c r="B70" s="35"/>
-      <c r="C70" s="35"/>
-      <c r="D70" s="36"/>
+      <c r="A70" s="35"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="37"/>
     </row>
     <row r="71" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="37"/>
-      <c r="B71" s="38"/>
-      <c r="C71" s="38"/>
-      <c r="D71" s="39"/>
+      <c r="A71" s="38"/>
+      <c r="B71" s="39"/>
+      <c r="C71" s="39"/>
+      <c r="D71" s="40"/>
     </row>
     <row r="72" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="34"/>
-      <c r="B72" s="35"/>
-      <c r="C72" s="35"/>
-      <c r="D72" s="36"/>
+      <c r="A72" s="35"/>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="37"/>
     </row>
     <row r="73" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="37"/>
-      <c r="B73" s="38"/>
-      <c r="C73" s="38"/>
-      <c r="D73" s="39"/>
+      <c r="A73" s="38"/>
+      <c r="B73" s="39"/>
+      <c r="C73" s="39"/>
+      <c r="D73" s="40"/>
     </row>
     <row r="74" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="34"/>
-      <c r="B74" s="35"/>
-      <c r="C74" s="35"/>
-      <c r="D74" s="36"/>
+      <c r="A74" s="35"/>
+      <c r="B74" s="36"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="37"/>
     </row>
     <row r="75" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="37"/>
-      <c r="B75" s="38"/>
-      <c r="C75" s="38"/>
-      <c r="D75" s="39"/>
+      <c r="A75" s="38"/>
+      <c r="B75" s="39"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="40"/>
     </row>
     <row r="76" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="34"/>
-      <c r="B76" s="35"/>
-      <c r="C76" s="35"/>
-      <c r="D76" s="36"/>
+      <c r="A76" s="35"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="36"/>
+      <c r="D76" s="37"/>
     </row>
     <row r="77" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="37"/>
-      <c r="B77" s="38"/>
-      <c r="C77" s="38"/>
-      <c r="D77" s="39"/>
+      <c r="A77" s="38"/>
+      <c r="B77" s="39"/>
+      <c r="C77" s="39"/>
+      <c r="D77" s="40"/>
     </row>
     <row r="78" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="34"/>
-      <c r="B78" s="35"/>
-      <c r="C78" s="35"/>
-      <c r="D78" s="36"/>
+      <c r="A78" s="35"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="37"/>
     </row>
     <row r="79" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="37"/>
-      <c r="B79" s="38"/>
-      <c r="C79" s="38"/>
-      <c r="D79" s="39"/>
+      <c r="A79" s="38"/>
+      <c r="B79" s="39"/>
+      <c r="C79" s="39"/>
+      <c r="D79" s="40"/>
     </row>
     <row r="80" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="34"/>
-      <c r="B80" s="35"/>
-      <c r="C80" s="35"/>
-      <c r="D80" s="36"/>
+      <c r="A80" s="35"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="36"/>
+      <c r="D80" s="37"/>
     </row>
     <row r="81" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="37"/>
-      <c r="B81" s="38"/>
-      <c r="C81" s="38"/>
-      <c r="D81" s="39"/>
+      <c r="A81" s="38"/>
+      <c r="B81" s="39"/>
+      <c r="C81" s="39"/>
+      <c r="D81" s="40"/>
     </row>
     <row r="82" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="34"/>
-      <c r="B82" s="35"/>
-      <c r="C82" s="35"/>
-      <c r="D82" s="36"/>
+      <c r="A82" s="35"/>
+      <c r="B82" s="36"/>
+      <c r="C82" s="36"/>
+      <c r="D82" s="37"/>
     </row>
     <row r="83" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="37"/>
-      <c r="B83" s="38"/>
-      <c r="C83" s="38"/>
-      <c r="D83" s="39"/>
+      <c r="A83" s="38"/>
+      <c r="B83" s="39"/>
+      <c r="C83" s="39"/>
+      <c r="D83" s="40"/>
     </row>
     <row r="84" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="34"/>
-      <c r="B84" s="35"/>
-      <c r="C84" s="35"/>
-      <c r="D84" s="36"/>
+      <c r="A84" s="35"/>
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="37"/>
     </row>
     <row r="85" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="37"/>
-      <c r="B85" s="38"/>
-      <c r="C85" s="38"/>
-      <c r="D85" s="39"/>
+      <c r="A85" s="38"/>
+      <c r="B85" s="39"/>
+      <c r="C85" s="39"/>
+      <c r="D85" s="40"/>
     </row>
     <row r="86" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="34"/>
-      <c r="B86" s="35"/>
-      <c r="C86" s="35"/>
-      <c r="D86" s="36"/>
+      <c r="A86" s="35"/>
+      <c r="B86" s="36"/>
+      <c r="C86" s="36"/>
+      <c r="D86" s="37"/>
     </row>
     <row r="87" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="37"/>
-      <c r="B87" s="38"/>
-      <c r="C87" s="38"/>
-      <c r="D87" s="39"/>
+      <c r="A87" s="38"/>
+      <c r="B87" s="39"/>
+      <c r="C87" s="39"/>
+      <c r="D87" s="40"/>
     </row>
     <row r="88" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="34"/>
-      <c r="B88" s="35"/>
-      <c r="C88" s="35"/>
-      <c r="D88" s="36"/>
+      <c r="A88" s="35"/>
+      <c r="B88" s="36"/>
+      <c r="C88" s="36"/>
+      <c r="D88" s="37"/>
     </row>
     <row r="89" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="37"/>
-      <c r="B89" s="38"/>
-      <c r="C89" s="38"/>
-      <c r="D89" s="39"/>
+      <c r="A89" s="38"/>
+      <c r="B89" s="39"/>
+      <c r="C89" s="39"/>
+      <c r="D89" s="40"/>
     </row>
     <row r="90" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="34"/>
-      <c r="B90" s="35"/>
-      <c r="C90" s="35"/>
-      <c r="D90" s="36"/>
+      <c r="A90" s="35"/>
+      <c r="B90" s="36"/>
+      <c r="C90" s="36"/>
+      <c r="D90" s="37"/>
     </row>
     <row r="91" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="37"/>
-      <c r="B91" s="38"/>
-      <c r="C91" s="38"/>
-      <c r="D91" s="39"/>
+      <c r="A91" s="38"/>
+      <c r="B91" s="39"/>
+      <c r="C91" s="39"/>
+      <c r="D91" s="40"/>
     </row>
     <row r="92" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="34"/>
-      <c r="B92" s="35"/>
-      <c r="C92" s="35"/>
-      <c r="D92" s="36"/>
+      <c r="A92" s="35"/>
+      <c r="B92" s="36"/>
+      <c r="C92" s="36"/>
+      <c r="D92" s="37"/>
     </row>
     <row r="93" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="37"/>
-      <c r="B93" s="38"/>
-      <c r="C93" s="38"/>
-      <c r="D93" s="39"/>
+      <c r="A93" s="38"/>
+      <c r="B93" s="39"/>
+      <c r="C93" s="39"/>
+      <c r="D93" s="40"/>
     </row>
     <row r="94" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="34"/>
-      <c r="B94" s="35"/>
-      <c r="C94" s="35"/>
-      <c r="D94" s="36"/>
+      <c r="A94" s="35"/>
+      <c r="B94" s="36"/>
+      <c r="C94" s="36"/>
+      <c r="D94" s="37"/>
     </row>
     <row r="95" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="37"/>
-      <c r="B95" s="38"/>
-      <c r="C95" s="38"/>
-      <c r="D95" s="39"/>
+      <c r="A95" s="38"/>
+      <c r="B95" s="39"/>
+      <c r="C95" s="39"/>
+      <c r="D95" s="40"/>
     </row>
     <row r="96" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="34"/>
-      <c r="B96" s="35"/>
-      <c r="C96" s="35"/>
-      <c r="D96" s="36"/>
+      <c r="A96" s="35"/>
+      <c r="B96" s="36"/>
+      <c r="C96" s="36"/>
+      <c r="D96" s="37"/>
     </row>
     <row r="97" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="37"/>
-      <c r="B97" s="38"/>
-      <c r="C97" s="38"/>
-      <c r="D97" s="39"/>
+      <c r="A97" s="38"/>
+      <c r="B97" s="39"/>
+      <c r="C97" s="39"/>
+      <c r="D97" s="40"/>
     </row>
     <row r="98" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="34"/>
-      <c r="B98" s="35"/>
-      <c r="C98" s="35"/>
-      <c r="D98" s="36"/>
+      <c r="A98" s="35"/>
+      <c r="B98" s="36"/>
+      <c r="C98" s="36"/>
+      <c r="D98" s="37"/>
     </row>
     <row r="99" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="37"/>
-      <c r="B99" s="38"/>
-      <c r="C99" s="38"/>
-      <c r="D99" s="39"/>
+      <c r="A99" s="38"/>
+      <c r="B99" s="39"/>
+      <c r="C99" s="39"/>
+      <c r="D99" s="40"/>
     </row>
     <row r="100" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="34"/>
-      <c r="B100" s="35"/>
-      <c r="C100" s="35"/>
-      <c r="D100" s="36"/>
+      <c r="A100" s="35"/>
+      <c r="B100" s="36"/>
+      <c r="C100" s="36"/>
+      <c r="D100" s="37"/>
     </row>
     <row r="101" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="37"/>
-      <c r="B101" s="38"/>
-      <c r="C101" s="38"/>
-      <c r="D101" s="39"/>
+      <c r="A101" s="38"/>
+      <c r="B101" s="39"/>
+      <c r="C101" s="39"/>
+      <c r="D101" s="40"/>
     </row>
     <row r="102" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="34"/>
-      <c r="B102" s="35"/>
-      <c r="C102" s="35"/>
-      <c r="D102" s="36"/>
+      <c r="A102" s="35"/>
+      <c r="B102" s="36"/>
+      <c r="C102" s="36"/>
+      <c r="D102" s="37"/>
     </row>
     <row r="103" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="37"/>
-      <c r="B103" s="38"/>
-      <c r="C103" s="38"/>
-      <c r="D103" s="39"/>
+      <c r="A103" s="38"/>
+      <c r="B103" s="39"/>
+      <c r="C103" s="39"/>
+      <c r="D103" s="40"/>
     </row>
     <row r="104" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="34"/>
-      <c r="B104" s="35"/>
-      <c r="C104" s="35"/>
-      <c r="D104" s="36"/>
+      <c r="A104" s="35"/>
+      <c r="B104" s="36"/>
+      <c r="C104" s="36"/>
+      <c r="D104" s="37"/>
     </row>
     <row r="105" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="37"/>
-      <c r="B105" s="38"/>
-      <c r="C105" s="38"/>
-      <c r="D105" s="39"/>
+      <c r="A105" s="38"/>
+      <c r="B105" s="39"/>
+      <c r="C105" s="39"/>
+      <c r="D105" s="40"/>
     </row>
     <row r="106" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="34"/>
-      <c r="B106" s="35"/>
-      <c r="C106" s="35"/>
-      <c r="D106" s="36"/>
+      <c r="A106" s="35"/>
+      <c r="B106" s="36"/>
+      <c r="C106" s="36"/>
+      <c r="D106" s="37"/>
     </row>
     <row r="107" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="37"/>
-      <c r="B107" s="38"/>
-      <c r="C107" s="38"/>
-      <c r="D107" s="39"/>
+      <c r="A107" s="38"/>
+      <c r="B107" s="39"/>
+      <c r="C107" s="39"/>
+      <c r="D107" s="40"/>
     </row>
     <row r="108" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="34"/>
-      <c r="B108" s="35"/>
-      <c r="C108" s="35"/>
-      <c r="D108" s="36"/>
+      <c r="A108" s="35"/>
+      <c r="B108" s="36"/>
+      <c r="C108" s="36"/>
+      <c r="D108" s="37"/>
     </row>
     <row r="109" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="37"/>
-      <c r="B109" s="38"/>
-      <c r="C109" s="38"/>
-      <c r="D109" s="39"/>
+      <c r="A109" s="38"/>
+      <c r="B109" s="39"/>
+      <c r="C109" s="39"/>
+      <c r="D109" s="40"/>
     </row>
     <row r="110" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="34"/>
-      <c r="B110" s="35"/>
-      <c r="C110" s="35"/>
-      <c r="D110" s="36"/>
+      <c r="A110" s="35"/>
+      <c r="B110" s="36"/>
+      <c r="C110" s="36"/>
+      <c r="D110" s="37"/>
     </row>
     <row r="111" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="37"/>
-      <c r="B111" s="38"/>
-      <c r="C111" s="38"/>
-      <c r="D111" s="39"/>
+      <c r="A111" s="38"/>
+      <c r="B111" s="39"/>
+      <c r="C111" s="39"/>
+      <c r="D111" s="40"/>
     </row>
     <row r="112" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="34"/>
-      <c r="B112" s="35"/>
-      <c r="C112" s="35"/>
-      <c r="D112" s="36"/>
+      <c r="A112" s="35"/>
+      <c r="B112" s="36"/>
+      <c r="C112" s="36"/>
+      <c r="D112" s="37"/>
     </row>
     <row r="113" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="37"/>
-      <c r="B113" s="38"/>
-      <c r="C113" s="38"/>
-      <c r="D113" s="39"/>
+      <c r="A113" s="38"/>
+      <c r="B113" s="39"/>
+      <c r="C113" s="39"/>
+      <c r="D113" s="40"/>
     </row>
     <row r="114" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="34"/>
-      <c r="B114" s="35"/>
-      <c r="C114" s="35"/>
-      <c r="D114" s="36"/>
+      <c r="A114" s="35"/>
+      <c r="B114" s="36"/>
+      <c r="C114" s="36"/>
+      <c r="D114" s="37"/>
     </row>
     <row r="115" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="37"/>
-      <c r="B115" s="38"/>
-      <c r="C115" s="38"/>
-      <c r="D115" s="39"/>
+      <c r="A115" s="38"/>
+      <c r="B115" s="39"/>
+      <c r="C115" s="39"/>
+      <c r="D115" s="40"/>
     </row>
     <row r="116" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="34"/>
-      <c r="B116" s="35"/>
-      <c r="C116" s="35"/>
-      <c r="D116" s="36"/>
+      <c r="A116" s="35"/>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="37"/>
     </row>
     <row r="117" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="37"/>
-      <c r="B117" s="38"/>
-      <c r="C117" s="38"/>
-      <c r="D117" s="39"/>
+      <c r="A117" s="38"/>
+      <c r="B117" s="39"/>
+      <c r="C117" s="39"/>
+      <c r="D117" s="40"/>
     </row>
     <row r="118" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="34"/>
-      <c r="B118" s="35"/>
-      <c r="C118" s="35"/>
-      <c r="D118" s="36"/>
+      <c r="A118" s="35"/>
+      <c r="B118" s="36"/>
+      <c r="C118" s="36"/>
+      <c r="D118" s="37"/>
     </row>
     <row r="119" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="37"/>
-      <c r="B119" s="38"/>
-      <c r="C119" s="38"/>
-      <c r="D119" s="39"/>
+      <c r="A119" s="38"/>
+      <c r="B119" s="39"/>
+      <c r="C119" s="39"/>
+      <c r="D119" s="40"/>
     </row>
     <row r="120" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="34"/>
-      <c r="B120" s="35"/>
-      <c r="C120" s="35"/>
-      <c r="D120" s="36"/>
+      <c r="A120" s="35"/>
+      <c r="B120" s="36"/>
+      <c r="C120" s="36"/>
+      <c r="D120" s="37"/>
     </row>
     <row r="121" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="37"/>
-      <c r="B121" s="38"/>
-      <c r="C121" s="38"/>
-      <c r="D121" s="39"/>
+      <c r="A121" s="38"/>
+      <c r="B121" s="39"/>
+      <c r="C121" s="39"/>
+      <c r="D121" s="40"/>
     </row>
     <row r="122" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="34"/>
-      <c r="B122" s="35"/>
-      <c r="C122" s="35"/>
-      <c r="D122" s="36"/>
+      <c r="A122" s="35"/>
+      <c r="B122" s="36"/>
+      <c r="C122" s="36"/>
+      <c r="D122" s="37"/>
     </row>
     <row r="123" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="37"/>
-      <c r="B123" s="38"/>
-      <c r="C123" s="38"/>
-      <c r="D123" s="39"/>
+      <c r="A123" s="38"/>
+      <c r="B123" s="39"/>
+      <c r="C123" s="39"/>
+      <c r="D123" s="40"/>
     </row>
     <row r="124" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="34"/>
-      <c r="B124" s="35"/>
-      <c r="C124" s="35"/>
-      <c r="D124" s="36"/>
+      <c r="A124" s="35"/>
+      <c r="B124" s="36"/>
+      <c r="C124" s="36"/>
+      <c r="D124" s="37"/>
     </row>
     <row r="125" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="37"/>
-      <c r="B125" s="38"/>
-      <c r="C125" s="38"/>
-      <c r="D125" s="39"/>
+      <c r="A125" s="38"/>
+      <c r="B125" s="39"/>
+      <c r="C125" s="39"/>
+      <c r="D125" s="40"/>
     </row>
     <row r="126" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="34"/>
-      <c r="B126" s="35"/>
-      <c r="C126" s="35"/>
-      <c r="D126" s="36"/>
+      <c r="A126" s="35"/>
+      <c r="B126" s="36"/>
+      <c r="C126" s="36"/>
+      <c r="D126" s="37"/>
     </row>
     <row r="127" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="37"/>
-      <c r="B127" s="38"/>
-      <c r="C127" s="38"/>
-      <c r="D127" s="39"/>
+      <c r="A127" s="38"/>
+      <c r="B127" s="39"/>
+      <c r="C127" s="39"/>
+      <c r="D127" s="40"/>
     </row>
     <row r="128" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="34"/>
-      <c r="B128" s="35"/>
-      <c r="C128" s="35"/>
-      <c r="D128" s="36"/>
+      <c r="A128" s="35"/>
+      <c r="B128" s="36"/>
+      <c r="C128" s="36"/>
+      <c r="D128" s="37"/>
     </row>
     <row r="129" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="37"/>
-      <c r="B129" s="38"/>
-      <c r="C129" s="38"/>
-      <c r="D129" s="39"/>
+      <c r="A129" s="38"/>
+      <c r="B129" s="39"/>
+      <c r="C129" s="39"/>
+      <c r="D129" s="40"/>
     </row>
     <row r="130" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="34"/>
-      <c r="B130" s="35"/>
-      <c r="C130" s="35"/>
-      <c r="D130" s="36"/>
+      <c r="A130" s="35"/>
+      <c r="B130" s="36"/>
+      <c r="C130" s="36"/>
+      <c r="D130" s="37"/>
     </row>
     <row r="131" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="37"/>
-      <c r="B131" s="38"/>
-      <c r="C131" s="38"/>
-      <c r="D131" s="39"/>
+      <c r="A131" s="38"/>
+      <c r="B131" s="39"/>
+      <c r="C131" s="39"/>
+      <c r="D131" s="40"/>
     </row>
     <row r="132" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="34"/>
-      <c r="B132" s="35"/>
-      <c r="C132" s="35"/>
-      <c r="D132" s="36"/>
+      <c r="A132" s="35"/>
+      <c r="B132" s="36"/>
+      <c r="C132" s="36"/>
+      <c r="D132" s="37"/>
     </row>
     <row r="133" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="37"/>
-      <c r="B133" s="38"/>
-      <c r="C133" s="38"/>
-      <c r="D133" s="39"/>
+      <c r="A133" s="38"/>
+      <c r="B133" s="39"/>
+      <c r="C133" s="39"/>
+      <c r="D133" s="40"/>
     </row>
     <row r="134" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="34"/>
-      <c r="B134" s="35"/>
-      <c r="C134" s="35"/>
-      <c r="D134" s="36"/>
+      <c r="A134" s="35"/>
+      <c r="B134" s="36"/>
+      <c r="C134" s="36"/>
+      <c r="D134" s="37"/>
     </row>
     <row r="135" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="37"/>
-      <c r="B135" s="38"/>
-      <c r="C135" s="38"/>
-      <c r="D135" s="39"/>
+      <c r="A135" s="38"/>
+      <c r="B135" s="39"/>
+      <c r="C135" s="39"/>
+      <c r="D135" s="40"/>
     </row>
     <row r="136" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="34"/>
-      <c r="B136" s="35"/>
-      <c r="C136" s="35"/>
-      <c r="D136" s="36"/>
+      <c r="A136" s="35"/>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="37"/>
     </row>
     <row r="137" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="37"/>
-      <c r="B137" s="38"/>
-      <c r="C137" s="38"/>
-      <c r="D137" s="39"/>
+      <c r="A137" s="38"/>
+      <c r="B137" s="39"/>
+      <c r="C137" s="39"/>
+      <c r="D137" s="40"/>
     </row>
     <row r="138" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="34"/>
-      <c r="B138" s="35"/>
-      <c r="C138" s="35"/>
-      <c r="D138" s="36"/>
+      <c r="A138" s="35"/>
+      <c r="B138" s="36"/>
+      <c r="C138" s="36"/>
+      <c r="D138" s="37"/>
     </row>
     <row r="139" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="37"/>
-      <c r="B139" s="38"/>
-      <c r="C139" s="38"/>
-      <c r="D139" s="39"/>
+      <c r="A139" s="38"/>
+      <c r="B139" s="39"/>
+      <c r="C139" s="39"/>
+      <c r="D139" s="40"/>
     </row>
     <row r="140" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="34"/>
-      <c r="B140" s="35"/>
-      <c r="C140" s="35"/>
-      <c r="D140" s="36"/>
+      <c r="A140" s="35"/>
+      <c r="B140" s="36"/>
+      <c r="C140" s="36"/>
+      <c r="D140" s="37"/>
     </row>
     <row r="141" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="37"/>
-      <c r="B141" s="38"/>
-      <c r="C141" s="38"/>
-      <c r="D141" s="39"/>
+      <c r="A141" s="38"/>
+      <c r="B141" s="39"/>
+      <c r="C141" s="39"/>
+      <c r="D141" s="40"/>
     </row>
     <row r="142" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="34"/>
-      <c r="B142" s="35"/>
-      <c r="C142" s="35"/>
-      <c r="D142" s="36"/>
+      <c r="A142" s="35"/>
+      <c r="B142" s="36"/>
+      <c r="C142" s="36"/>
+      <c r="D142" s="37"/>
     </row>
     <row r="143" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="37"/>
-      <c r="B143" s="38"/>
-      <c r="C143" s="38"/>
-      <c r="D143" s="39"/>
+      <c r="A143" s="38"/>
+      <c r="B143" s="39"/>
+      <c r="C143" s="39"/>
+      <c r="D143" s="40"/>
     </row>
     <row r="144" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="34"/>
-      <c r="B144" s="35"/>
-      <c r="C144" s="35"/>
-      <c r="D144" s="36"/>
+      <c r="A144" s="35"/>
+      <c r="B144" s="36"/>
+      <c r="C144" s="36"/>
+      <c r="D144" s="37"/>
     </row>
     <row r="145" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="37"/>
-      <c r="B145" s="38"/>
-      <c r="C145" s="38"/>
-      <c r="D145" s="39"/>
+      <c r="A145" s="38"/>
+      <c r="B145" s="39"/>
+      <c r="C145" s="39"/>
+      <c r="D145" s="40"/>
     </row>
     <row r="146" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="34"/>
-      <c r="B146" s="35"/>
-      <c r="C146" s="35"/>
-      <c r="D146" s="36"/>
+      <c r="A146" s="35"/>
+      <c r="B146" s="36"/>
+      <c r="C146" s="36"/>
+      <c r="D146" s="37"/>
     </row>
     <row r="147" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="37"/>
-      <c r="B147" s="38"/>
-      <c r="C147" s="38"/>
-      <c r="D147" s="39"/>
+      <c r="A147" s="38"/>
+      <c r="B147" s="39"/>
+      <c r="C147" s="39"/>
+      <c r="D147" s="40"/>
     </row>
     <row r="148" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="34"/>
-      <c r="B148" s="35"/>
-      <c r="C148" s="35"/>
-      <c r="D148" s="36"/>
+      <c r="A148" s="35"/>
+      <c r="B148" s="36"/>
+      <c r="C148" s="36"/>
+      <c r="D148" s="37"/>
     </row>
     <row r="149" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="37"/>
-      <c r="B149" s="38"/>
-      <c r="C149" s="38"/>
-      <c r="D149" s="39"/>
+      <c r="A149" s="38"/>
+      <c r="B149" s="39"/>
+      <c r="C149" s="39"/>
+      <c r="D149" s="40"/>
     </row>
     <row r="150" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="34"/>
-      <c r="B150" s="35"/>
-      <c r="C150" s="35"/>
-      <c r="D150" s="36"/>
+      <c r="A150" s="35"/>
+      <c r="B150" s="36"/>
+      <c r="C150" s="36"/>
+      <c r="D150" s="37"/>
     </row>
     <row r="151" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="37"/>
-      <c r="B151" s="38"/>
-      <c r="C151" s="38"/>
-      <c r="D151" s="39"/>
+      <c r="A151" s="38"/>
+      <c r="B151" s="39"/>
+      <c r="C151" s="39"/>
+      <c r="D151" s="40"/>
     </row>
     <row r="152" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="34"/>
-      <c r="B152" s="35"/>
-      <c r="C152" s="35"/>
-      <c r="D152" s="36"/>
+      <c r="A152" s="35"/>
+      <c r="B152" s="36"/>
+      <c r="C152" s="36"/>
+      <c r="D152" s="37"/>
     </row>
     <row r="153" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="37"/>
-      <c r="B153" s="38"/>
-      <c r="C153" s="38"/>
-      <c r="D153" s="39"/>
+      <c r="A153" s="38"/>
+      <c r="B153" s="39"/>
+      <c r="C153" s="39"/>
+      <c r="D153" s="40"/>
     </row>
     <row r="154" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="34"/>
-      <c r="B154" s="35"/>
-      <c r="C154" s="35"/>
-      <c r="D154" s="36"/>
+      <c r="A154" s="35"/>
+      <c r="B154" s="36"/>
+      <c r="C154" s="36"/>
+      <c r="D154" s="37"/>
     </row>
     <row r="155" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="37"/>
-      <c r="B155" s="38"/>
-      <c r="C155" s="38"/>
-      <c r="D155" s="39"/>
+      <c r="A155" s="38"/>
+      <c r="B155" s="39"/>
+      <c r="C155" s="39"/>
+      <c r="D155" s="40"/>
     </row>
     <row r="156" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="34"/>
-      <c r="B156" s="35"/>
-      <c r="C156" s="35"/>
-      <c r="D156" s="36"/>
+      <c r="A156" s="35"/>
+      <c r="B156" s="36"/>
+      <c r="C156" s="36"/>
+      <c r="D156" s="37"/>
     </row>
     <row r="157" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="37"/>
-      <c r="B157" s="38"/>
-      <c r="C157" s="38"/>
-      <c r="D157" s="39"/>
+      <c r="A157" s="38"/>
+      <c r="B157" s="39"/>
+      <c r="C157" s="39"/>
+      <c r="D157" s="40"/>
     </row>
     <row r="158" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="34"/>
-      <c r="B158" s="35"/>
-      <c r="C158" s="35"/>
-      <c r="D158" s="36"/>
+      <c r="A158" s="35"/>
+      <c r="B158" s="36"/>
+      <c r="C158" s="36"/>
+      <c r="D158" s="37"/>
     </row>
     <row r="159" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="37"/>
-      <c r="B159" s="38"/>
-      <c r="C159" s="38"/>
-      <c r="D159" s="39"/>
+      <c r="A159" s="38"/>
+      <c r="B159" s="39"/>
+      <c r="C159" s="39"/>
+      <c r="D159" s="40"/>
     </row>
     <row r="160" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="34"/>
-      <c r="B160" s="35"/>
-      <c r="C160" s="35"/>
-      <c r="D160" s="36"/>
+      <c r="A160" s="35"/>
+      <c r="B160" s="36"/>
+      <c r="C160" s="36"/>
+      <c r="D160" s="37"/>
     </row>
     <row r="161" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="37"/>
-      <c r="B161" s="38"/>
-      <c r="C161" s="38"/>
-      <c r="D161" s="39"/>
+      <c r="A161" s="38"/>
+      <c r="B161" s="39"/>
+      <c r="C161" s="39"/>
+      <c r="D161" s="40"/>
     </row>
     <row r="162" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="34"/>
-      <c r="B162" s="35"/>
-      <c r="C162" s="35"/>
-      <c r="D162" s="36"/>
+      <c r="A162" s="35"/>
+      <c r="B162" s="36"/>
+      <c r="C162" s="36"/>
+      <c r="D162" s="37"/>
     </row>
     <row r="163" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="37"/>
-      <c r="B163" s="38"/>
-      <c r="C163" s="38"/>
-      <c r="D163" s="39"/>
+      <c r="A163" s="38"/>
+      <c r="B163" s="39"/>
+      <c r="C163" s="39"/>
+      <c r="D163" s="40"/>
     </row>
     <row r="164" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="34"/>
-      <c r="B164" s="35"/>
-      <c r="C164" s="35"/>
-      <c r="D164" s="36"/>
+      <c r="A164" s="35"/>
+      <c r="B164" s="36"/>
+      <c r="C164" s="36"/>
+      <c r="D164" s="37"/>
     </row>
     <row r="165" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="37"/>
-      <c r="B165" s="38"/>
-      <c r="C165" s="38"/>
-      <c r="D165" s="39"/>
+      <c r="A165" s="38"/>
+      <c r="B165" s="39"/>
+      <c r="C165" s="39"/>
+      <c r="D165" s="40"/>
     </row>
     <row r="166" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="34"/>
-      <c r="B166" s="35"/>
-      <c r="C166" s="35"/>
-      <c r="D166" s="36"/>
+      <c r="A166" s="35"/>
+      <c r="B166" s="36"/>
+      <c r="C166" s="36"/>
+      <c r="D166" s="37"/>
     </row>
     <row r="167" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="37"/>
-      <c r="B167" s="38"/>
-      <c r="C167" s="38"/>
-      <c r="D167" s="39"/>
+      <c r="A167" s="38"/>
+      <c r="B167" s="39"/>
+      <c r="C167" s="39"/>
+      <c r="D167" s="40"/>
     </row>
     <row r="168" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="34"/>
-      <c r="B168" s="35"/>
-      <c r="C168" s="35"/>
-      <c r="D168" s="36"/>
+      <c r="A168" s="35"/>
+      <c r="B168" s="36"/>
+      <c r="C168" s="36"/>
+      <c r="D168" s="37"/>
     </row>
     <row r="169" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="37"/>
-      <c r="B169" s="38"/>
-      <c r="C169" s="38"/>
-      <c r="D169" s="39"/>
+      <c r="A169" s="38"/>
+      <c r="B169" s="39"/>
+      <c r="C169" s="39"/>
+      <c r="D169" s="40"/>
     </row>
     <row r="170" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="34"/>
-      <c r="B170" s="35"/>
-      <c r="C170" s="35"/>
-      <c r="D170" s="36"/>
+      <c r="A170" s="35"/>
+      <c r="B170" s="36"/>
+      <c r="C170" s="36"/>
+      <c r="D170" s="37"/>
     </row>
     <row r="171" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="37"/>
-      <c r="B171" s="38"/>
-      <c r="C171" s="38"/>
-      <c r="D171" s="39"/>
+      <c r="A171" s="38"/>
+      <c r="B171" s="39"/>
+      <c r="C171" s="39"/>
+      <c r="D171" s="40"/>
     </row>
     <row r="172" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="34"/>
-      <c r="B172" s="35"/>
-      <c r="C172" s="35"/>
-      <c r="D172" s="36"/>
+      <c r="A172" s="35"/>
+      <c r="B172" s="36"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="37"/>
     </row>
     <row r="173" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="37"/>
-      <c r="B173" s="38"/>
-      <c r="C173" s="38"/>
-      <c r="D173" s="39"/>
+      <c r="A173" s="38"/>
+      <c r="B173" s="39"/>
+      <c r="C173" s="39"/>
+      <c r="D173" s="40"/>
     </row>
     <row r="174" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="34"/>
-      <c r="B174" s="35"/>
-      <c r="C174" s="35"/>
-      <c r="D174" s="36"/>
+      <c r="A174" s="35"/>
+      <c r="B174" s="36"/>
+      <c r="C174" s="36"/>
+      <c r="D174" s="37"/>
     </row>
     <row r="175" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="37"/>
-      <c r="B175" s="38"/>
-      <c r="C175" s="38"/>
-      <c r="D175" s="39"/>
+      <c r="A175" s="38"/>
+      <c r="B175" s="39"/>
+      <c r="C175" s="39"/>
+      <c r="D175" s="40"/>
     </row>
     <row r="176" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="34"/>
-      <c r="B176" s="35"/>
-      <c r="C176" s="35"/>
-      <c r="D176" s="36"/>
+      <c r="A176" s="35"/>
+      <c r="B176" s="36"/>
+      <c r="C176" s="36"/>
+      <c r="D176" s="37"/>
     </row>
     <row r="177" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="37"/>
-      <c r="B177" s="38"/>
-      <c r="C177" s="38"/>
-      <c r="D177" s="39"/>
+      <c r="A177" s="38"/>
+      <c r="B177" s="39"/>
+      <c r="C177" s="39"/>
+      <c r="D177" s="40"/>
     </row>
     <row r="178" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="34"/>
-      <c r="B178" s="35"/>
-      <c r="C178" s="35"/>
-      <c r="D178" s="36"/>
+      <c r="A178" s="35"/>
+      <c r="B178" s="36"/>
+      <c r="C178" s="36"/>
+      <c r="D178" s="37"/>
     </row>
     <row r="179" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="37"/>
-      <c r="B179" s="38"/>
-      <c r="C179" s="38"/>
-      <c r="D179" s="39"/>
+      <c r="A179" s="38"/>
+      <c r="B179" s="39"/>
+      <c r="C179" s="39"/>
+      <c r="D179" s="40"/>
     </row>
     <row r="180" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="34"/>
-      <c r="B180" s="35"/>
-      <c r="C180" s="35"/>
-      <c r="D180" s="36"/>
+      <c r="A180" s="35"/>
+      <c r="B180" s="36"/>
+      <c r="C180" s="36"/>
+      <c r="D180" s="37"/>
     </row>
     <row r="181" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="37"/>
-      <c r="B181" s="38"/>
-      <c r="C181" s="38"/>
-      <c r="D181" s="39"/>
+      <c r="A181" s="38"/>
+      <c r="B181" s="39"/>
+      <c r="C181" s="39"/>
+      <c r="D181" s="40"/>
     </row>
     <row r="182" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="34"/>
-      <c r="B182" s="35"/>
-      <c r="C182" s="35"/>
-      <c r="D182" s="36"/>
+      <c r="A182" s="35"/>
+      <c r="B182" s="36"/>
+      <c r="C182" s="36"/>
+      <c r="D182" s="37"/>
     </row>
     <row r="183" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="37"/>
-      <c r="B183" s="38"/>
-      <c r="C183" s="38"/>
-      <c r="D183" s="39"/>
+      <c r="A183" s="38"/>
+      <c r="B183" s="39"/>
+      <c r="C183" s="39"/>
+      <c r="D183" s="40"/>
     </row>
     <row r="184" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="34"/>
-      <c r="B184" s="35"/>
-      <c r="C184" s="35"/>
-      <c r="D184" s="36"/>
+      <c r="A184" s="35"/>
+      <c r="B184" s="36"/>
+      <c r="C184" s="36"/>
+      <c r="D184" s="37"/>
     </row>
     <row r="185" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="37"/>
-      <c r="B185" s="38"/>
-      <c r="C185" s="38"/>
-      <c r="D185" s="39"/>
+      <c r="A185" s="38"/>
+      <c r="B185" s="39"/>
+      <c r="C185" s="39"/>
+      <c r="D185" s="40"/>
     </row>
     <row r="186" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="34"/>
-      <c r="B186" s="35"/>
-      <c r="C186" s="35"/>
-      <c r="D186" s="36"/>
+      <c r="A186" s="35"/>
+      <c r="B186" s="36"/>
+      <c r="C186" s="36"/>
+      <c r="D186" s="37"/>
     </row>
     <row r="187" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="37"/>
-      <c r="B187" s="38"/>
-      <c r="C187" s="38"/>
-      <c r="D187" s="39"/>
+      <c r="A187" s="38"/>
+      <c r="B187" s="39"/>
+      <c r="C187" s="39"/>
+      <c r="D187" s="40"/>
     </row>
     <row r="188" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="34"/>
-      <c r="B188" s="35"/>
-      <c r="C188" s="35"/>
-      <c r="D188" s="36"/>
+      <c r="A188" s="35"/>
+      <c r="B188" s="36"/>
+      <c r="C188" s="36"/>
+      <c r="D188" s="37"/>
     </row>
     <row r="189" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="37"/>
-      <c r="B189" s="38"/>
-      <c r="C189" s="38"/>
-      <c r="D189" s="39"/>
+      <c r="A189" s="38"/>
+      <c r="B189" s="39"/>
+      <c r="C189" s="39"/>
+      <c r="D189" s="40"/>
     </row>
     <row r="190" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="34"/>
-      <c r="B190" s="35"/>
-      <c r="C190" s="35"/>
-      <c r="D190" s="36"/>
+      <c r="A190" s="35"/>
+      <c r="B190" s="36"/>
+      <c r="C190" s="36"/>
+      <c r="D190" s="37"/>
     </row>
     <row r="191" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="37"/>
-      <c r="B191" s="38"/>
-      <c r="C191" s="38"/>
-      <c r="D191" s="39"/>
+      <c r="A191" s="38"/>
+      <c r="B191" s="39"/>
+      <c r="C191" s="39"/>
+      <c r="D191" s="40"/>
     </row>
     <row r="192" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="34"/>
-      <c r="B192" s="35"/>
-      <c r="C192" s="35"/>
-      <c r="D192" s="36"/>
+      <c r="A192" s="35"/>
+      <c r="B192" s="36"/>
+      <c r="C192" s="36"/>
+      <c r="D192" s="37"/>
     </row>
     <row r="193" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="37"/>
-      <c r="B193" s="38"/>
-      <c r="C193" s="38"/>
-      <c r="D193" s="39"/>
+      <c r="A193" s="38"/>
+      <c r="B193" s="39"/>
+      <c r="C193" s="39"/>
+      <c r="D193" s="40"/>
     </row>
     <row r="194" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="34"/>
-      <c r="B194" s="35"/>
-      <c r="C194" s="35"/>
-      <c r="D194" s="36"/>
+      <c r="A194" s="35"/>
+      <c r="B194" s="36"/>
+      <c r="C194" s="36"/>
+      <c r="D194" s="37"/>
     </row>
     <row r="195" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="37"/>
-      <c r="B195" s="38"/>
-      <c r="C195" s="38"/>
-      <c r="D195" s="39"/>
+      <c r="A195" s="38"/>
+      <c r="B195" s="39"/>
+      <c r="C195" s="39"/>
+      <c r="D195" s="40"/>
     </row>
     <row r="196" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="34"/>
-      <c r="B196" s="35"/>
-      <c r="C196" s="35"/>
-      <c r="D196" s="36"/>
+      <c r="A196" s="35"/>
+      <c r="B196" s="36"/>
+      <c r="C196" s="36"/>
+      <c r="D196" s="37"/>
     </row>
     <row r="197" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="37"/>
-      <c r="B197" s="38"/>
-      <c r="C197" s="38"/>
-      <c r="D197" s="39"/>
+      <c r="A197" s="38"/>
+      <c r="B197" s="39"/>
+      <c r="C197" s="39"/>
+      <c r="D197" s="40"/>
     </row>
     <row r="198" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="34"/>
-      <c r="B198" s="35"/>
-      <c r="C198" s="35"/>
-      <c r="D198" s="36"/>
+      <c r="A198" s="35"/>
+      <c r="B198" s="36"/>
+      <c r="C198" s="36"/>
+      <c r="D198" s="37"/>
     </row>
     <row r="199" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="37"/>
-      <c r="B199" s="38"/>
-      <c r="C199" s="38"/>
-      <c r="D199" s="39"/>
+      <c r="A199" s="38"/>
+      <c r="B199" s="39"/>
+      <c r="C199" s="39"/>
+      <c r="D199" s="40"/>
     </row>
     <row r="200" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="34"/>
-      <c r="B200" s="35"/>
-      <c r="C200" s="35"/>
-      <c r="D200" s="36"/>
+      <c r="A200" s="35"/>
+      <c r="B200" s="36"/>
+      <c r="C200" s="36"/>
+      <c r="D200" s="37"/>
     </row>
     <row r="201" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="37"/>
-      <c r="B201" s="38"/>
-      <c r="C201" s="38"/>
-      <c r="D201" s="39"/>
+      <c r="A201" s="38"/>
+      <c r="B201" s="39"/>
+      <c r="C201" s="39"/>
+      <c r="D201" s="40"/>
     </row>
     <row r="202" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="34"/>
-      <c r="B202" s="35"/>
-      <c r="C202" s="35"/>
-      <c r="D202" s="36"/>
+      <c r="A202" s="35"/>
+      <c r="B202" s="36"/>
+      <c r="C202" s="36"/>
+      <c r="D202" s="37"/>
     </row>
     <row r="203" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="37"/>
-      <c r="B203" s="38"/>
-      <c r="C203" s="38"/>
-      <c r="D203" s="39"/>
+      <c r="A203" s="38"/>
+      <c r="B203" s="39"/>
+      <c r="C203" s="39"/>
+      <c r="D203" s="40"/>
     </row>
     <row r="204" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="34"/>
-      <c r="B204" s="35"/>
-      <c r="C204" s="35"/>
-      <c r="D204" s="36"/>
+      <c r="A204" s="35"/>
+      <c r="B204" s="36"/>
+      <c r="C204" s="36"/>
+      <c r="D204" s="37"/>
     </row>
     <row r="205" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="37"/>
-      <c r="B205" s="38"/>
-      <c r="C205" s="38"/>
-      <c r="D205" s="39"/>
+      <c r="A205" s="38"/>
+      <c r="B205" s="39"/>
+      <c r="C205" s="39"/>
+      <c r="D205" s="40"/>
     </row>
     <row r="206" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="34"/>
-      <c r="B206" s="35"/>
-      <c r="C206" s="35"/>
-      <c r="D206" s="36"/>
+      <c r="A206" s="35"/>
+      <c r="B206" s="36"/>
+      <c r="C206" s="36"/>
+      <c r="D206" s="37"/>
     </row>
     <row r="207" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="37"/>
-      <c r="B207" s="38"/>
-      <c r="C207" s="38"/>
-      <c r="D207" s="39"/>
+      <c r="A207" s="38"/>
+      <c r="B207" s="39"/>
+      <c r="C207" s="39"/>
+      <c r="D207" s="40"/>
     </row>
     <row r="208" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="34"/>
-      <c r="B208" s="35"/>
-      <c r="C208" s="35"/>
-      <c r="D208" s="36"/>
+      <c r="A208" s="35"/>
+      <c r="B208" s="36"/>
+      <c r="C208" s="36"/>
+      <c r="D208" s="37"/>
     </row>
     <row r="209" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="37"/>
-      <c r="B209" s="38"/>
-      <c r="C209" s="38"/>
-      <c r="D209" s="39"/>
+      <c r="A209" s="38"/>
+      <c r="B209" s="39"/>
+      <c r="C209" s="39"/>
+      <c r="D209" s="40"/>
     </row>
     <row r="210" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="34"/>
-      <c r="B210" s="35"/>
-      <c r="C210" s="35"/>
-      <c r="D210" s="36"/>
+      <c r="A210" s="35"/>
+      <c r="B210" s="36"/>
+      <c r="C210" s="36"/>
+      <c r="D210" s="37"/>
     </row>
     <row r="211" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="37"/>
-      <c r="B211" s="38"/>
-      <c r="C211" s="38"/>
-      <c r="D211" s="39"/>
+      <c r="A211" s="38"/>
+      <c r="B211" s="39"/>
+      <c r="C211" s="39"/>
+      <c r="D211" s="40"/>
     </row>
     <row r="212" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="34"/>
-      <c r="B212" s="35"/>
-      <c r="C212" s="35"/>
-      <c r="D212" s="36"/>
+      <c r="A212" s="35"/>
+      <c r="B212" s="36"/>
+      <c r="C212" s="36"/>
+      <c r="D212" s="37"/>
     </row>
     <row r="213" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="37"/>
-      <c r="B213" s="38"/>
-      <c r="C213" s="38"/>
-      <c r="D213" s="39"/>
+      <c r="A213" s="38"/>
+      <c r="B213" s="39"/>
+      <c r="C213" s="39"/>
+      <c r="D213" s="40"/>
     </row>
     <row r="214" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="34"/>
-      <c r="B214" s="35"/>
-      <c r="C214" s="35"/>
-      <c r="D214" s="36"/>
+      <c r="A214" s="35"/>
+      <c r="B214" s="36"/>
+      <c r="C214" s="36"/>
+      <c r="D214" s="37"/>
     </row>
     <row r="215" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="37"/>
-      <c r="B215" s="38"/>
-      <c r="C215" s="38"/>
-      <c r="D215" s="39"/>
+      <c r="A215" s="38"/>
+      <c r="B215" s="39"/>
+      <c r="C215" s="39"/>
+      <c r="D215" s="40"/>
     </row>
     <row r="216" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="34"/>
-      <c r="B216" s="35"/>
-      <c r="C216" s="35"/>
-      <c r="D216" s="36"/>
+      <c r="A216" s="35"/>
+      <c r="B216" s="36"/>
+      <c r="C216" s="36"/>
+      <c r="D216" s="37"/>
     </row>
     <row r="217" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="37"/>
-      <c r="B217" s="38"/>
-      <c r="C217" s="38"/>
-      <c r="D217" s="39"/>
+      <c r="A217" s="38"/>
+      <c r="B217" s="39"/>
+      <c r="C217" s="39"/>
+      <c r="D217" s="40"/>
     </row>
     <row r="218" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="34"/>
-      <c r="B218" s="35"/>
-      <c r="C218" s="35"/>
-      <c r="D218" s="36"/>
+      <c r="A218" s="35"/>
+      <c r="B218" s="36"/>
+      <c r="C218" s="36"/>
+      <c r="D218" s="37"/>
     </row>
     <row r="219" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="37"/>
-      <c r="B219" s="38"/>
-      <c r="C219" s="38"/>
-      <c r="D219" s="39"/>
+      <c r="A219" s="38"/>
+      <c r="B219" s="39"/>
+      <c r="C219" s="39"/>
+      <c r="D219" s="40"/>
     </row>
     <row r="220" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="34"/>
-      <c r="B220" s="35"/>
-      <c r="C220" s="35"/>
-      <c r="D220" s="36"/>
+      <c r="A220" s="35"/>
+      <c r="B220" s="36"/>
+      <c r="C220" s="36"/>
+      <c r="D220" s="37"/>
     </row>
     <row r="221" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="37"/>
-      <c r="B221" s="38"/>
-      <c r="C221" s="38"/>
-      <c r="D221" s="39"/>
+      <c r="A221" s="38"/>
+      <c r="B221" s="39"/>
+      <c r="C221" s="39"/>
+      <c r="D221" s="40"/>
     </row>
     <row r="222" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="34"/>
-      <c r="B222" s="35"/>
-      <c r="C222" s="35"/>
-      <c r="D222" s="36"/>
+      <c r="A222" s="35"/>
+      <c r="B222" s="36"/>
+      <c r="C222" s="36"/>
+      <c r="D222" s="37"/>
     </row>
     <row r="223" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="37"/>
-      <c r="B223" s="38"/>
-      <c r="C223" s="38"/>
-      <c r="D223" s="39"/>
+      <c r="A223" s="38"/>
+      <c r="B223" s="39"/>
+      <c r="C223" s="39"/>
+      <c r="D223" s="40"/>
     </row>
     <row r="224" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="34"/>
-      <c r="B224" s="35"/>
-      <c r="C224" s="35"/>
-      <c r="D224" s="36"/>
+      <c r="A224" s="35"/>
+      <c r="B224" s="36"/>
+      <c r="C224" s="36"/>
+      <c r="D224" s="37"/>
     </row>
     <row r="225" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="37"/>
-      <c r="B225" s="38"/>
-      <c r="C225" s="38"/>
-      <c r="D225" s="39"/>
+      <c r="A225" s="38"/>
+      <c r="B225" s="39"/>
+      <c r="C225" s="39"/>
+      <c r="D225" s="40"/>
     </row>
     <row r="226" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="34"/>
-      <c r="B226" s="35"/>
-      <c r="C226" s="35"/>
-      <c r="D226" s="36"/>
+      <c r="A226" s="35"/>
+      <c r="B226" s="36"/>
+      <c r="C226" s="36"/>
+      <c r="D226" s="37"/>
     </row>
     <row r="227" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="37"/>
-      <c r="B227" s="38"/>
-      <c r="C227" s="38"/>
-      <c r="D227" s="39"/>
+      <c r="A227" s="38"/>
+      <c r="B227" s="39"/>
+      <c r="C227" s="39"/>
+      <c r="D227" s="40"/>
     </row>
     <row r="228" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="34"/>
-      <c r="B228" s="35"/>
-      <c r="C228" s="35"/>
-      <c r="D228" s="36"/>
+      <c r="A228" s="35"/>
+      <c r="B228" s="36"/>
+      <c r="C228" s="36"/>
+      <c r="D228" s="37"/>
     </row>
     <row r="229" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="37"/>
-      <c r="B229" s="38"/>
-      <c r="C229" s="38"/>
-      <c r="D229" s="39"/>
+      <c r="A229" s="38"/>
+      <c r="B229" s="39"/>
+      <c r="C229" s="39"/>
+      <c r="D229" s="40"/>
     </row>
     <row r="230" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="34"/>
-      <c r="B230" s="35"/>
-      <c r="C230" s="35"/>
-      <c r="D230" s="36"/>
+      <c r="A230" s="35"/>
+      <c r="B230" s="36"/>
+      <c r="C230" s="36"/>
+      <c r="D230" s="37"/>
     </row>
     <row r="231" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="37"/>
-      <c r="B231" s="38"/>
-      <c r="C231" s="38"/>
-      <c r="D231" s="39"/>
+      <c r="A231" s="38"/>
+      <c r="B231" s="39"/>
+      <c r="C231" s="39"/>
+      <c r="D231" s="40"/>
     </row>
     <row r="232" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="34"/>
-      <c r="B232" s="35"/>
-      <c r="C232" s="35"/>
-      <c r="D232" s="36"/>
+      <c r="A232" s="35"/>
+      <c r="B232" s="36"/>
+      <c r="C232" s="36"/>
+      <c r="D232" s="37"/>
     </row>
     <row r="233" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="37"/>
-      <c r="B233" s="38"/>
-      <c r="C233" s="38"/>
-      <c r="D233" s="39"/>
+      <c r="A233" s="38"/>
+      <c r="B233" s="39"/>
+      <c r="C233" s="39"/>
+      <c r="D233" s="40"/>
     </row>
     <row r="234" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="34"/>
-      <c r="B234" s="35"/>
-      <c r="C234" s="35"/>
-      <c r="D234" s="36"/>
+      <c r="A234" s="35"/>
+      <c r="B234" s="36"/>
+      <c r="C234" s="36"/>
+      <c r="D234" s="37"/>
     </row>
     <row r="235" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="37"/>
-      <c r="B235" s="38"/>
-      <c r="C235" s="38"/>
-      <c r="D235" s="39"/>
+      <c r="A235" s="38"/>
+      <c r="B235" s="39"/>
+      <c r="C235" s="39"/>
+      <c r="D235" s="40"/>
     </row>
     <row r="236" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="34"/>
-      <c r="B236" s="35"/>
-      <c r="C236" s="35"/>
-      <c r="D236" s="36"/>
+      <c r="A236" s="35"/>
+      <c r="B236" s="36"/>
+      <c r="C236" s="36"/>
+      <c r="D236" s="37"/>
     </row>
     <row r="237" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="37"/>
-      <c r="B237" s="38"/>
-      <c r="C237" s="38"/>
-      <c r="D237" s="39"/>
+      <c r="A237" s="38"/>
+      <c r="B237" s="39"/>
+      <c r="C237" s="39"/>
+      <c r="D237" s="40"/>
     </row>
     <row r="238" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="34"/>
-      <c r="B238" s="35"/>
-      <c r="C238" s="35"/>
-      <c r="D238" s="36"/>
+      <c r="A238" s="35"/>
+      <c r="B238" s="36"/>
+      <c r="C238" s="36"/>
+      <c r="D238" s="37"/>
     </row>
     <row r="239" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="37"/>
-      <c r="B239" s="38"/>
-      <c r="C239" s="38"/>
-      <c r="D239" s="39"/>
+      <c r="A239" s="38"/>
+      <c r="B239" s="39"/>
+      <c r="C239" s="39"/>
+      <c r="D239" s="40"/>
     </row>
     <row r="240" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="34"/>
-      <c r="B240" s="35"/>
-      <c r="C240" s="35"/>
-      <c r="D240" s="36"/>
+      <c r="A240" s="35"/>
+      <c r="B240" s="36"/>
+      <c r="C240" s="36"/>
+      <c r="D240" s="37"/>
     </row>
     <row r="241" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="37"/>
-      <c r="B241" s="38"/>
-      <c r="C241" s="38"/>
-      <c r="D241" s="39"/>
+      <c r="A241" s="38"/>
+      <c r="B241" s="39"/>
+      <c r="C241" s="39"/>
+      <c r="D241" s="40"/>
     </row>
     <row r="242" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="34"/>
-      <c r="B242" s="35"/>
-      <c r="C242" s="35"/>
-      <c r="D242" s="36"/>
+      <c r="A242" s="35"/>
+      <c r="B242" s="36"/>
+      <c r="C242" s="36"/>
+      <c r="D242" s="37"/>
     </row>
     <row r="243" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="37"/>
-      <c r="B243" s="38"/>
-      <c r="C243" s="38"/>
-      <c r="D243" s="39"/>
+      <c r="A243" s="38"/>
+      <c r="B243" s="39"/>
+      <c r="C243" s="39"/>
+      <c r="D243" s="40"/>
     </row>
     <row r="244" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="34"/>
-      <c r="B244" s="35"/>
-      <c r="C244" s="35"/>
-      <c r="D244" s="36"/>
+      <c r="A244" s="35"/>
+      <c r="B244" s="36"/>
+      <c r="C244" s="36"/>
+      <c r="D244" s="37"/>
     </row>
     <row r="245" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="37"/>
-      <c r="B245" s="38"/>
-      <c r="C245" s="38"/>
-      <c r="D245" s="39"/>
+      <c r="A245" s="38"/>
+      <c r="B245" s="39"/>
+      <c r="C245" s="39"/>
+      <c r="D245" s="40"/>
     </row>
     <row r="246" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="34"/>
-      <c r="B246" s="35"/>
-      <c r="C246" s="35"/>
-      <c r="D246" s="36"/>
+      <c r="A246" s="35"/>
+      <c r="B246" s="36"/>
+      <c r="C246" s="36"/>
+      <c r="D246" s="37"/>
     </row>
     <row r="247" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="37"/>
-      <c r="B247" s="38"/>
-      <c r="C247" s="38"/>
-      <c r="D247" s="39"/>
+      <c r="A247" s="38"/>
+      <c r="B247" s="39"/>
+      <c r="C247" s="39"/>
+      <c r="D247" s="40"/>
     </row>
     <row r="248" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="34"/>
-      <c r="B248" s="35"/>
-      <c r="C248" s="35"/>
-      <c r="D248" s="36"/>
+      <c r="A248" s="35"/>
+      <c r="B248" s="36"/>
+      <c r="C248" s="36"/>
+      <c r="D248" s="37"/>
     </row>
     <row r="249" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="37"/>
-      <c r="B249" s="38"/>
-      <c r="C249" s="38"/>
-      <c r="D249" s="39"/>
+      <c r="A249" s="38"/>
+      <c r="B249" s="39"/>
+      <c r="C249" s="39"/>
+      <c r="D249" s="40"/>
     </row>
     <row r="250" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="34"/>
-      <c r="B250" s="35"/>
-      <c r="C250" s="35"/>
-      <c r="D250" s="36"/>
+      <c r="A250" s="35"/>
+      <c r="B250" s="36"/>
+      <c r="C250" s="36"/>
+      <c r="D250" s="37"/>
     </row>
     <row r="251" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="37"/>
-      <c r="B251" s="38"/>
-      <c r="C251" s="38"/>
-      <c r="D251" s="39"/>
+      <c r="A251" s="38"/>
+      <c r="B251" s="39"/>
+      <c r="C251" s="39"/>
+      <c r="D251" s="40"/>
     </row>
     <row r="252" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="34"/>
-      <c r="B252" s="35"/>
-      <c r="C252" s="35"/>
-      <c r="D252" s="36"/>
+      <c r="A252" s="35"/>
+      <c r="B252" s="36"/>
+      <c r="C252" s="36"/>
+      <c r="D252" s="37"/>
     </row>
     <row r="253" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="37"/>
-      <c r="B253" s="38"/>
-      <c r="C253" s="38"/>
-      <c r="D253" s="39"/>
+      <c r="A253" s="38"/>
+      <c r="B253" s="39"/>
+      <c r="C253" s="39"/>
+      <c r="D253" s="40"/>
     </row>
     <row r="254" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="34"/>
-      <c r="B254" s="35"/>
-      <c r="C254" s="35"/>
-      <c r="D254" s="36"/>
+      <c r="A254" s="35"/>
+      <c r="B254" s="36"/>
+      <c r="C254" s="36"/>
+      <c r="D254" s="37"/>
     </row>
     <row r="255" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="37"/>
-      <c r="B255" s="38"/>
-      <c r="C255" s="38"/>
-      <c r="D255" s="39"/>
+      <c r="A255" s="38"/>
+      <c r="B255" s="39"/>
+      <c r="C255" s="39"/>
+      <c r="D255" s="40"/>
     </row>
     <row r="256" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="34"/>
-      <c r="B256" s="35"/>
-      <c r="C256" s="35"/>
-      <c r="D256" s="36"/>
+      <c r="A256" s="35"/>
+      <c r="B256" s="36"/>
+      <c r="C256" s="36"/>
+      <c r="D256" s="37"/>
     </row>
     <row r="257" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="37"/>
-      <c r="B257" s="38"/>
-      <c r="C257" s="38"/>
-      <c r="D257" s="39"/>
+      <c r="A257" s="38"/>
+      <c r="B257" s="39"/>
+      <c r="C257" s="39"/>
+      <c r="D257" s="40"/>
     </row>
     <row r="258" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="34"/>
-      <c r="B258" s="35"/>
-      <c r="C258" s="35"/>
-      <c r="D258" s="36"/>
+      <c r="A258" s="35"/>
+      <c r="B258" s="36"/>
+      <c r="C258" s="36"/>
+      <c r="D258" s="37"/>
     </row>
     <row r="259" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="37"/>
-      <c r="B259" s="38"/>
-      <c r="C259" s="38"/>
-      <c r="D259" s="39"/>
+      <c r="A259" s="38"/>
+      <c r="B259" s="39"/>
+      <c r="C259" s="39"/>
+      <c r="D259" s="40"/>
     </row>
     <row r="260" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="34"/>
-      <c r="B260" s="35"/>
-      <c r="C260" s="35"/>
-      <c r="D260" s="36"/>
+      <c r="A260" s="35"/>
+      <c r="B260" s="36"/>
+      <c r="C260" s="36"/>
+      <c r="D260" s="37"/>
     </row>
     <row r="261" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="37"/>
-      <c r="B261" s="38"/>
-      <c r="C261" s="38"/>
-      <c r="D261" s="39"/>
+      <c r="A261" s="38"/>
+      <c r="B261" s="39"/>
+      <c r="C261" s="39"/>
+      <c r="D261" s="40"/>
     </row>
     <row r="262" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="34"/>
-      <c r="B262" s="35"/>
-      <c r="C262" s="35"/>
-      <c r="D262" s="36"/>
+      <c r="A262" s="35"/>
+      <c r="B262" s="36"/>
+      <c r="C262" s="36"/>
+      <c r="D262" s="37"/>
     </row>
     <row r="263" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="37"/>
-      <c r="B263" s="38"/>
-      <c r="C263" s="38"/>
-      <c r="D263" s="39"/>
+      <c r="A263" s="38"/>
+      <c r="B263" s="39"/>
+      <c r="C263" s="39"/>
+      <c r="D263" s="40"/>
     </row>
     <row r="264" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="34"/>
-      <c r="B264" s="35"/>
-      <c r="C264" s="35"/>
-      <c r="D264" s="36"/>
+      <c r="A264" s="35"/>
+      <c r="B264" s="36"/>
+      <c r="C264" s="36"/>
+      <c r="D264" s="37"/>
     </row>
     <row r="265" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="37"/>
-      <c r="B265" s="38"/>
-      <c r="C265" s="38"/>
-      <c r="D265" s="39"/>
+      <c r="A265" s="38"/>
+      <c r="B265" s="39"/>
+      <c r="C265" s="39"/>
+      <c r="D265" s="40"/>
     </row>
     <row r="266" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="34"/>
-      <c r="B266" s="35"/>
-      <c r="C266" s="35"/>
-      <c r="D266" s="36"/>
+      <c r="A266" s="35"/>
+      <c r="B266" s="36"/>
+      <c r="C266" s="36"/>
+      <c r="D266" s="37"/>
     </row>
     <row r="267" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="37"/>
-      <c r="B267" s="38"/>
-      <c r="C267" s="38"/>
-      <c r="D267" s="39"/>
+      <c r="A267" s="38"/>
+      <c r="B267" s="39"/>
+      <c r="C267" s="39"/>
+      <c r="D267" s="40"/>
     </row>
     <row r="268" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="34"/>
-      <c r="B268" s="35"/>
-      <c r="C268" s="35"/>
-      <c r="D268" s="36"/>
+      <c r="A268" s="35"/>
+      <c r="B268" s="36"/>
+      <c r="C268" s="36"/>
+      <c r="D268" s="37"/>
     </row>
     <row r="269" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="37"/>
-      <c r="B269" s="38"/>
-      <c r="C269" s="38"/>
-      <c r="D269" s="39"/>
+      <c r="A269" s="38"/>
+      <c r="B269" s="39"/>
+      <c r="C269" s="39"/>
+      <c r="D269" s="40"/>
     </row>
     <row r="270" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="34"/>
-      <c r="B270" s="35"/>
-      <c r="C270" s="35"/>
-      <c r="D270" s="36"/>
+      <c r="A270" s="35"/>
+      <c r="B270" s="36"/>
+      <c r="C270" s="36"/>
+      <c r="D270" s="37"/>
     </row>
     <row r="271" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="37"/>
-      <c r="B271" s="38"/>
-      <c r="C271" s="38"/>
-      <c r="D271" s="39"/>
+      <c r="A271" s="38"/>
+      <c r="B271" s="39"/>
+      <c r="C271" s="39"/>
+      <c r="D271" s="40"/>
     </row>
     <row r="272" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="34"/>
-      <c r="B272" s="35"/>
-      <c r="C272" s="35"/>
-      <c r="D272" s="36"/>
+      <c r="A272" s="35"/>
+      <c r="B272" s="36"/>
+      <c r="C272" s="36"/>
+      <c r="D272" s="37"/>
     </row>
     <row r="273" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="37"/>
-      <c r="B273" s="38"/>
-      <c r="C273" s="38"/>
-      <c r="D273" s="39"/>
+      <c r="A273" s="38"/>
+      <c r="B273" s="39"/>
+      <c r="C273" s="39"/>
+      <c r="D273" s="40"/>
     </row>
     <row r="274" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="34"/>
-      <c r="B274" s="35"/>
-      <c r="C274" s="35"/>
-      <c r="D274" s="36"/>
+      <c r="A274" s="35"/>
+      <c r="B274" s="36"/>
+      <c r="C274" s="36"/>
+      <c r="D274" s="37"/>
     </row>
     <row r="275" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="37"/>
-      <c r="B275" s="38"/>
-      <c r="C275" s="38"/>
-      <c r="D275" s="39"/>
+      <c r="A275" s="38"/>
+      <c r="B275" s="39"/>
+      <c r="C275" s="39"/>
+      <c r="D275" s="40"/>
     </row>
     <row r="276" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="34"/>
-      <c r="B276" s="35"/>
-      <c r="C276" s="35"/>
-      <c r="D276" s="36"/>
+      <c r="A276" s="35"/>
+      <c r="B276" s="36"/>
+      <c r="C276" s="36"/>
+      <c r="D276" s="37"/>
     </row>
     <row r="277" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="37"/>
-      <c r="B277" s="38"/>
-      <c r="C277" s="38"/>
-      <c r="D277" s="39"/>
+      <c r="A277" s="38"/>
+      <c r="B277" s="39"/>
+      <c r="C277" s="39"/>
+      <c r="D277" s="40"/>
     </row>
     <row r="278" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="34"/>
-      <c r="B278" s="35"/>
-      <c r="C278" s="35"/>
-      <c r="D278" s="36"/>
+      <c r="A278" s="35"/>
+      <c r="B278" s="36"/>
+      <c r="C278" s="36"/>
+      <c r="D278" s="37"/>
     </row>
     <row r="279" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="37"/>
-      <c r="B279" s="38"/>
-      <c r="C279" s="38"/>
-      <c r="D279" s="39"/>
+      <c r="A279" s="38"/>
+      <c r="B279" s="39"/>
+      <c r="C279" s="39"/>
+      <c r="D279" s="40"/>
     </row>
     <row r="280" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="34"/>
-      <c r="B280" s="35"/>
-      <c r="C280" s="35"/>
-      <c r="D280" s="36"/>
+      <c r="A280" s="35"/>
+      <c r="B280" s="36"/>
+      <c r="C280" s="36"/>
+      <c r="D280" s="37"/>
     </row>
     <row r="281" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="37"/>
-      <c r="B281" s="38"/>
-      <c r="C281" s="38"/>
-      <c r="D281" s="39"/>
+      <c r="A281" s="38"/>
+      <c r="B281" s="39"/>
+      <c r="C281" s="39"/>
+      <c r="D281" s="40"/>
     </row>
     <row r="282" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="34"/>
-      <c r="B282" s="35"/>
-      <c r="C282" s="35"/>
-      <c r="D282" s="36"/>
+      <c r="A282" s="35"/>
+      <c r="B282" s="36"/>
+      <c r="C282" s="36"/>
+      <c r="D282" s="37"/>
     </row>
     <row r="283" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="37"/>
-      <c r="B283" s="38"/>
-      <c r="C283" s="38"/>
-      <c r="D283" s="39"/>
+      <c r="A283" s="38"/>
+      <c r="B283" s="39"/>
+      <c r="C283" s="39"/>
+      <c r="D283" s="40"/>
     </row>
     <row r="284" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="34"/>
-      <c r="B284" s="35"/>
-      <c r="C284" s="35"/>
-      <c r="D284" s="36"/>
+      <c r="A284" s="35"/>
+      <c r="B284" s="36"/>
+      <c r="C284" s="36"/>
+      <c r="D284" s="37"/>
     </row>
     <row r="285" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="37"/>
-      <c r="B285" s="38"/>
-      <c r="C285" s="38"/>
-      <c r="D285" s="39"/>
+      <c r="A285" s="38"/>
+      <c r="B285" s="39"/>
+      <c r="C285" s="39"/>
+      <c r="D285" s="40"/>
     </row>
     <row r="286" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="34"/>
-      <c r="B286" s="35"/>
-      <c r="C286" s="35"/>
-      <c r="D286" s="36"/>
+      <c r="A286" s="35"/>
+      <c r="B286" s="36"/>
+      <c r="C286" s="36"/>
+      <c r="D286" s="37"/>
     </row>
     <row r="287" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="37"/>
-      <c r="B287" s="38"/>
-      <c r="C287" s="38"/>
-      <c r="D287" s="39"/>
+      <c r="A287" s="38"/>
+      <c r="B287" s="39"/>
+      <c r="C287" s="39"/>
+      <c r="D287" s="40"/>
     </row>
     <row r="288" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="34"/>
-      <c r="B288" s="35"/>
-      <c r="C288" s="35"/>
-      <c r="D288" s="36"/>
+      <c r="A288" s="35"/>
+      <c r="B288" s="36"/>
+      <c r="C288" s="36"/>
+      <c r="D288" s="37"/>
     </row>
     <row r="289" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="37"/>
-      <c r="B289" s="38"/>
-      <c r="C289" s="38"/>
-      <c r="D289" s="39"/>
+      <c r="A289" s="38"/>
+      <c r="B289" s="39"/>
+      <c r="C289" s="39"/>
+      <c r="D289" s="40"/>
     </row>
     <row r="290" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="34"/>
-      <c r="B290" s="35"/>
-      <c r="C290" s="35"/>
-      <c r="D290" s="36"/>
+      <c r="A290" s="35"/>
+      <c r="B290" s="36"/>
+      <c r="C290" s="36"/>
+      <c r="D290" s="37"/>
     </row>
     <row r="291" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="37"/>
-      <c r="B291" s="38"/>
-      <c r="C291" s="38"/>
-      <c r="D291" s="39"/>
+      <c r="A291" s="38"/>
+      <c r="B291" s="39"/>
+      <c r="C291" s="39"/>
+      <c r="D291" s="40"/>
     </row>
     <row r="292" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="34"/>
-      <c r="B292" s="35"/>
-      <c r="C292" s="35"/>
-      <c r="D292" s="36"/>
+      <c r="A292" s="35"/>
+      <c r="B292" s="36"/>
+      <c r="C292" s="36"/>
+      <c r="D292" s="37"/>
     </row>
     <row r="293" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="37"/>
-      <c r="B293" s="38"/>
-      <c r="C293" s="38"/>
-      <c r="D293" s="39"/>
+      <c r="A293" s="38"/>
+      <c r="B293" s="39"/>
+      <c r="C293" s="39"/>
+      <c r="D293" s="40"/>
     </row>
     <row r="294" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="34"/>
-      <c r="B294" s="35"/>
-      <c r="C294" s="35"/>
-      <c r="D294" s="36"/>
+      <c r="A294" s="35"/>
+      <c r="B294" s="36"/>
+      <c r="C294" s="36"/>
+      <c r="D294" s="37"/>
     </row>
     <row r="295" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="37"/>
-      <c r="B295" s="38"/>
-      <c r="C295" s="38"/>
-      <c r="D295" s="39"/>
+      <c r="A295" s="38"/>
+      <c r="B295" s="39"/>
+      <c r="C295" s="39"/>
+      <c r="D295" s="40"/>
     </row>
     <row r="296" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="34"/>
-      <c r="B296" s="35"/>
-      <c r="C296" s="35"/>
-      <c r="D296" s="36"/>
+      <c r="A296" s="35"/>
+      <c r="B296" s="36"/>
+      <c r="C296" s="36"/>
+      <c r="D296" s="37"/>
     </row>
     <row r="297" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="37"/>
-      <c r="B297" s="38"/>
-      <c r="C297" s="38"/>
-      <c r="D297" s="39"/>
+      <c r="A297" s="38"/>
+      <c r="B297" s="39"/>
+      <c r="C297" s="39"/>
+      <c r="D297" s="40"/>
     </row>
     <row r="298" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="34"/>
-      <c r="B298" s="35"/>
-      <c r="C298" s="35"/>
-      <c r="D298" s="36"/>
+      <c r="A298" s="35"/>
+      <c r="B298" s="36"/>
+      <c r="C298" s="36"/>
+      <c r="D298" s="37"/>
     </row>
     <row r="299" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="37"/>
-      <c r="B299" s="38"/>
-      <c r="C299" s="38"/>
-      <c r="D299" s="39"/>
+      <c r="A299" s="38"/>
+      <c r="B299" s="39"/>
+      <c r="C299" s="39"/>
+      <c r="D299" s="40"/>
     </row>
     <row r="300" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="34"/>
-      <c r="B300" s="35"/>
-      <c r="C300" s="35"/>
-      <c r="D300" s="36"/>
+      <c r="A300" s="35"/>
+      <c r="B300" s="36"/>
+      <c r="C300" s="36"/>
+      <c r="D300" s="37"/>
     </row>
     <row r="301" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="37"/>
-      <c r="B301" s="38"/>
-      <c r="C301" s="38"/>
-      <c r="D301" s="39"/>
+      <c r="A301" s="38"/>
+      <c r="B301" s="39"/>
+      <c r="C301" s="39"/>
+      <c r="D301" s="40"/>
     </row>
     <row r="302" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="34"/>
-      <c r="B302" s="35"/>
-      <c r="C302" s="35"/>
-      <c r="D302" s="36"/>
+      <c r="A302" s="35"/>
+      <c r="B302" s="36"/>
+      <c r="C302" s="36"/>
+      <c r="D302" s="37"/>
     </row>
     <row r="303" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="37"/>
-      <c r="B303" s="38"/>
-      <c r="C303" s="38"/>
-      <c r="D303" s="39"/>
+      <c r="A303" s="38"/>
+      <c r="B303" s="39"/>
+      <c r="C303" s="39"/>
+      <c r="D303" s="40"/>
     </row>
     <row r="304" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="34"/>
-      <c r="B304" s="35"/>
-      <c r="C304" s="35"/>
-      <c r="D304" s="36"/>
+      <c r="A304" s="35"/>
+      <c r="B304" s="36"/>
+      <c r="C304" s="36"/>
+      <c r="D304" s="37"/>
     </row>
     <row r="305" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="37"/>
-      <c r="B305" s="38"/>
-      <c r="C305" s="38"/>
-      <c r="D305" s="39"/>
+      <c r="A305" s="38"/>
+      <c r="B305" s="39"/>
+      <c r="C305" s="39"/>
+      <c r="D305" s="40"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" autoFilter="false"/>
@@ -6371,12 +6373,12 @@
       <c r="D4" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="E4" s="40" t="str">
+      <c r="E4" s="41" t="str">
         <f aca="false">CHOOSE($B$4,"January","February","March","April","May","June","July","August","September","October","November","December")&amp;" "&amp;$D$4</f>
         <v>August 2026</v>
       </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -6403,24 +6405,24 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="41" t="s">
+    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41" t="s">
+      <c r="D6" s="42"/>
+      <c r="E6" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41" t="s">
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="I6" s="41"/>
+      <c r="I6" s="42"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -6428,28 +6430,28 @@
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="42" t="n">
+    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="43" t="n">
         <f aca="false">SUM('Budget Setup'!$B$7:$B$10)</f>
         <v>4550</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42" t="n">
+      <c r="B7" s="43"/>
+      <c r="C7" s="43" t="n">
         <f aca="false">SUM('Budget Setup'!$B$15:$B$34)</f>
         <v>4455</v>
       </c>
-      <c r="D7" s="42"/>
-      <c r="E7" s="43" t="n">
+      <c r="D7" s="43"/>
+      <c r="E7" s="44" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1))</f>
         <v>1783.5</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="44" t="n">
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="45" t="n">
         <f aca="false">C7-E7</f>
         <v>2671.5</v>
       </c>
-      <c r="I7" s="44"/>
+      <c r="I7" s="45"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -6510,7 +6512,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
         <v>33</v>
       </c>
@@ -6538,23 +6540,23 @@
       <c r="O11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45" t="str">
+      <c r="A12" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A15="","",'Budget Setup'!A15)</f>
         <v>Housing</v>
       </c>
-      <c r="B12" s="46" t="n">
+      <c r="B12" s="47" t="n">
         <f aca="false">IF($A12="","",'Budget Setup'!B15)</f>
         <v>1600</v>
       </c>
-      <c r="C12" s="46" t="n">
+      <c r="C12" s="47" t="n">
         <f aca="false">IF($A12="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A12,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v>1600</v>
       </c>
-      <c r="D12" s="46" t="n">
+      <c r="D12" s="47" t="n">
         <f aca="false">IF($A12="","",$B12-$C12)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="47" t="n">
+      <c r="E12" s="48" t="n">
         <f aca="false">IF(OR($A12="",$B12=0),"",$C12/$B12)</f>
         <v>1</v>
       </c>
@@ -6570,23 +6572,23 @@
       <c r="O12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="45" t="str">
+      <c r="A13" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A16="","",'Budget Setup'!A16)</f>
         <v>Groceries</v>
       </c>
-      <c r="B13" s="46" t="n">
+      <c r="B13" s="47" t="n">
         <f aca="false">IF($A13="","",'Budget Setup'!B16)</f>
         <v>550</v>
       </c>
-      <c r="C13" s="46" t="n">
+      <c r="C13" s="47" t="n">
         <f aca="false">IF($A13="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A13,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v>84.2</v>
       </c>
-      <c r="D13" s="46" t="n">
+      <c r="D13" s="47" t="n">
         <f aca="false">IF($A13="","",$B13-$C13)</f>
         <v>465.8</v>
       </c>
-      <c r="E13" s="47" t="n">
+      <c r="E13" s="48" t="n">
         <f aca="false">IF(OR($A13="",$B13=0),"",$C13/$B13)</f>
         <v>0.153090909090909</v>
       </c>
@@ -6602,23 +6604,23 @@
       <c r="O13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="45" t="str">
+      <c r="A14" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A17="","",'Budget Setup'!A17)</f>
         <v>Dining out</v>
       </c>
-      <c r="B14" s="46" t="n">
+      <c r="B14" s="47" t="n">
         <f aca="false">IF($A14="","",'Budget Setup'!B17)</f>
         <v>250</v>
       </c>
-      <c r="C14" s="46" t="n">
+      <c r="C14" s="47" t="n">
         <f aca="false">IF($A14="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A14,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v>56.8</v>
       </c>
-      <c r="D14" s="46" t="n">
+      <c r="D14" s="47" t="n">
         <f aca="false">IF($A14="","",$B14-$C14)</f>
         <v>193.2</v>
       </c>
-      <c r="E14" s="47" t="n">
+      <c r="E14" s="48" t="n">
         <f aca="false">IF(OR($A14="",$B14=0),"",$C14/$B14)</f>
         <v>0.2272</v>
       </c>
@@ -6634,23 +6636,23 @@
       <c r="O14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="45" t="str">
+      <c r="A15" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A18="","",'Budget Setup'!A18)</f>
         <v>Transport</v>
       </c>
-      <c r="B15" s="46" t="n">
+      <c r="B15" s="47" t="n">
         <f aca="false">IF($A15="","",'Budget Setup'!B18)</f>
         <v>200</v>
       </c>
-      <c r="C15" s="46" t="n">
+      <c r="C15" s="47" t="n">
         <f aca="false">IF($A15="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A15,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v>42.5</v>
       </c>
-      <c r="D15" s="46" t="n">
+      <c r="D15" s="47" t="n">
         <f aca="false">IF($A15="","",$B15-$C15)</f>
         <v>157.5</v>
       </c>
-      <c r="E15" s="47" t="n">
+      <c r="E15" s="48" t="n">
         <f aca="false">IF(OR($A15="",$B15=0),"",$C15/$B15)</f>
         <v>0.2125</v>
       </c>
@@ -6666,23 +6668,23 @@
       <c r="O15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="45" t="str">
+      <c r="A16" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A19="","",'Budget Setup'!A19)</f>
         <v>Utilities</v>
       </c>
-      <c r="B16" s="46" t="n">
+      <c r="B16" s="47" t="n">
         <f aca="false">IF($A16="","",'Budget Setup'!B19)</f>
         <v>180</v>
       </c>
-      <c r="C16" s="46" t="n">
+      <c r="C16" s="47" t="n">
         <f aca="false">IF($A16="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A16,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v>0</v>
       </c>
-      <c r="D16" s="46" t="n">
+      <c r="D16" s="47" t="n">
         <f aca="false">IF($A16="","",$B16-$C16)</f>
         <v>180</v>
       </c>
-      <c r="E16" s="47" t="n">
+      <c r="E16" s="48" t="n">
         <f aca="false">IF(OR($A16="",$B16=0),"",$C16/$B16)</f>
         <v>0</v>
       </c>
@@ -6698,23 +6700,23 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="45" t="str">
+      <c r="A17" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A20="","",'Budget Setup'!A20)</f>
         <v>Phone &amp; internet</v>
       </c>
-      <c r="B17" s="46" t="n">
+      <c r="B17" s="47" t="n">
         <f aca="false">IF($A17="","",'Budget Setup'!B20)</f>
         <v>95</v>
       </c>
-      <c r="C17" s="46" t="n">
+      <c r="C17" s="47" t="n">
         <f aca="false">IF($A17="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A17,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v>0</v>
       </c>
-      <c r="D17" s="46" t="n">
+      <c r="D17" s="47" t="n">
         <f aca="false">IF($A17="","",$B17-$C17)</f>
         <v>95</v>
       </c>
-      <c r="E17" s="47" t="n">
+      <c r="E17" s="48" t="n">
         <f aca="false">IF(OR($A17="",$B17=0),"",$C17/$B17)</f>
         <v>0</v>
       </c>
@@ -6730,23 +6732,23 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="45" t="str">
+      <c r="A18" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A21="","",'Budget Setup'!A21)</f>
         <v>Insurance</v>
       </c>
-      <c r="B18" s="46" t="n">
+      <c r="B18" s="47" t="n">
         <f aca="false">IF($A18="","",'Budget Setup'!B21)</f>
         <v>140</v>
       </c>
-      <c r="C18" s="46" t="n">
+      <c r="C18" s="47" t="n">
         <f aca="false">IF($A18="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A18,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v>0</v>
       </c>
-      <c r="D18" s="46" t="n">
+      <c r="D18" s="47" t="n">
         <f aca="false">IF($A18="","",$B18-$C18)</f>
         <v>140</v>
       </c>
-      <c r="E18" s="47" t="n">
+      <c r="E18" s="48" t="n">
         <f aca="false">IF(OR($A18="",$B18=0),"",$C18/$B18)</f>
         <v>0</v>
       </c>
@@ -6762,23 +6764,23 @@
       <c r="O18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="45" t="str">
+      <c r="A19" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A22="","",'Budget Setup'!A22)</f>
         <v>Health &amp; fitness</v>
       </c>
-      <c r="B19" s="46" t="n">
+      <c r="B19" s="47" t="n">
         <f aca="false">IF($A19="","",'Budget Setup'!B22)</f>
         <v>90</v>
       </c>
-      <c r="C19" s="46" t="n">
+      <c r="C19" s="47" t="n">
         <f aca="false">IF($A19="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A19,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v>0</v>
       </c>
-      <c r="D19" s="46" t="n">
+      <c r="D19" s="47" t="n">
         <f aca="false">IF($A19="","",$B19-$C19)</f>
         <v>90</v>
       </c>
-      <c r="E19" s="47" t="n">
+      <c r="E19" s="48" t="n">
         <f aca="false">IF(OR($A19="",$B19=0),"",$C19/$B19)</f>
         <v>0</v>
       </c>
@@ -6794,23 +6796,23 @@
       <c r="O19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="45" t="str">
+      <c r="A20" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A23="","",'Budget Setup'!A23)</f>
         <v>Entertainment</v>
       </c>
-      <c r="B20" s="46" t="n">
+      <c r="B20" s="47" t="n">
         <f aca="false">IF($A20="","",'Budget Setup'!B23)</f>
         <v>120</v>
       </c>
-      <c r="C20" s="46" t="n">
+      <c r="C20" s="47" t="n">
         <f aca="false">IF($A20="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A20,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v>0</v>
       </c>
-      <c r="D20" s="46" t="n">
+      <c r="D20" s="47" t="n">
         <f aca="false">IF($A20="","",$B20-$C20)</f>
         <v>120</v>
       </c>
-      <c r="E20" s="47" t="n">
+      <c r="E20" s="48" t="n">
         <f aca="false">IF(OR($A20="",$B20=0),"",$C20/$B20)</f>
         <v>0</v>
       </c>
@@ -6826,23 +6828,23 @@
       <c r="O20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="45" t="str">
+      <c r="A21" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A24="","",'Budget Setup'!A24)</f>
         <v>Subscriptions</v>
       </c>
-      <c r="B21" s="46" t="n">
+      <c r="B21" s="47" t="n">
         <f aca="false">IF($A21="","",'Budget Setup'!B24)</f>
         <v>60</v>
       </c>
-      <c r="C21" s="46" t="n">
+      <c r="C21" s="47" t="n">
         <f aca="false">IF($A21="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A21,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v>0</v>
       </c>
-      <c r="D21" s="46" t="n">
+      <c r="D21" s="47" t="n">
         <f aca="false">IF($A21="","",$B21-$C21)</f>
         <v>60</v>
       </c>
-      <c r="E21" s="47" t="n">
+      <c r="E21" s="48" t="n">
         <f aca="false">IF(OR($A21="",$B21=0),"",$C21/$B21)</f>
         <v>0</v>
       </c>
@@ -6858,23 +6860,23 @@
       <c r="O21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="str">
+      <c r="A22" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A25="","",'Budget Setup'!A25)</f>
         <v>Shopping</v>
       </c>
-      <c r="B22" s="46" t="n">
+      <c r="B22" s="47" t="n">
         <f aca="false">IF($A22="","",'Budget Setup'!B25)</f>
         <v>150</v>
       </c>
-      <c r="C22" s="46" t="n">
+      <c r="C22" s="47" t="n">
         <f aca="false">IF($A22="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A22,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v>0</v>
       </c>
-      <c r="D22" s="46" t="n">
+      <c r="D22" s="47" t="n">
         <f aca="false">IF($A22="","",$B22-$C22)</f>
         <v>150</v>
       </c>
-      <c r="E22" s="47" t="n">
+      <c r="E22" s="48" t="n">
         <f aca="false">IF(OR($A22="",$B22=0),"",$C22/$B22)</f>
         <v>0</v>
       </c>
@@ -6890,23 +6892,23 @@
       <c r="O22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="45" t="str">
+      <c r="A23" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A26="","",'Budget Setup'!A26)</f>
         <v>Personal care</v>
       </c>
-      <c r="B23" s="46" t="n">
+      <c r="B23" s="47" t="n">
         <f aca="false">IF($A23="","",'Budget Setup'!B26)</f>
         <v>70</v>
       </c>
-      <c r="C23" s="46" t="n">
+      <c r="C23" s="47" t="n">
         <f aca="false">IF($A23="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A23,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v>0</v>
       </c>
-      <c r="D23" s="46" t="n">
+      <c r="D23" s="47" t="n">
         <f aca="false">IF($A23="","",$B23-$C23)</f>
         <v>70</v>
       </c>
-      <c r="E23" s="47" t="n">
+      <c r="E23" s="48" t="n">
         <f aca="false">IF(OR($A23="",$B23=0),"",$C23/$B23)</f>
         <v>0</v>
       </c>
@@ -6922,23 +6924,23 @@
       <c r="O23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="45" t="str">
+      <c r="A24" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A27="","",'Budget Setup'!A27)</f>
         <v>Savings &amp; investing</v>
       </c>
-      <c r="B24" s="46" t="n">
+      <c r="B24" s="47" t="n">
         <f aca="false">IF($A24="","",'Budget Setup'!B27)</f>
         <v>500</v>
       </c>
-      <c r="C24" s="46" t="n">
+      <c r="C24" s="47" t="n">
         <f aca="false">IF($A24="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A24,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v>0</v>
       </c>
-      <c r="D24" s="46" t="n">
+      <c r="D24" s="47" t="n">
         <f aca="false">IF($A24="","",$B24-$C24)</f>
         <v>500</v>
       </c>
-      <c r="E24" s="47" t="n">
+      <c r="E24" s="48" t="n">
         <f aca="false">IF(OR($A24="",$B24=0),"",$C24/$B24)</f>
         <v>0</v>
       </c>
@@ -6954,23 +6956,23 @@
       <c r="O24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="45" t="str">
+      <c r="A25" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A28="","",'Budget Setup'!A28)</f>
         <v>Debt payments</v>
       </c>
-      <c r="B25" s="46" t="n">
+      <c r="B25" s="47" t="n">
         <f aca="false">IF($A25="","",'Budget Setup'!B28)</f>
         <v>300</v>
       </c>
-      <c r="C25" s="46" t="n">
+      <c r="C25" s="47" t="n">
         <f aca="false">IF($A25="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A25,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v>0</v>
       </c>
-      <c r="D25" s="46" t="n">
+      <c r="D25" s="47" t="n">
         <f aca="false">IF($A25="","",$B25-$C25)</f>
         <v>300</v>
       </c>
-      <c r="E25" s="47" t="n">
+      <c r="E25" s="48" t="n">
         <f aca="false">IF(OR($A25="",$B25=0),"",$C25/$B25)</f>
         <v>0</v>
       </c>
@@ -6986,23 +6988,23 @@
       <c r="O25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="45" t="str">
+      <c r="A26" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A29="","",'Budget Setup'!A29)</f>
         <v>Everything else</v>
       </c>
-      <c r="B26" s="46" t="n">
+      <c r="B26" s="47" t="n">
         <f aca="false">IF($A26="","",'Budget Setup'!B29)</f>
         <v>150</v>
       </c>
-      <c r="C26" s="46" t="n">
+      <c r="C26" s="47" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v>0</v>
       </c>
-      <c r="D26" s="46" t="n">
+      <c r="D26" s="47" t="n">
         <f aca="false">IF($A26="","",$B26-$C26)</f>
         <v>150</v>
       </c>
-      <c r="E26" s="47" t="n">
+      <c r="E26" s="48" t="n">
         <f aca="false">IF(OR($A26="",$B26=0),"",$C26/$B26)</f>
         <v>0</v>
       </c>
@@ -7018,23 +7020,23 @@
       <c r="O26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="45" t="str">
+      <c r="A27" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A30="","",'Budget Setup'!A30)</f>
         <v/>
       </c>
-      <c r="B27" s="46" t="str">
+      <c r="B27" s="47" t="str">
         <f aca="false">IF($A27="","",'Budget Setup'!B30)</f>
         <v/>
       </c>
-      <c r="C27" s="46" t="str">
+      <c r="C27" s="47" t="str">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v/>
       </c>
-      <c r="D27" s="46" t="str">
+      <c r="D27" s="47" t="str">
         <f aca="false">IF($A27="","",$B27-$C27)</f>
         <v/>
       </c>
-      <c r="E27" s="47" t="str">
+      <c r="E27" s="48" t="str">
         <f aca="false">IF(OR($A27="",$B27=0),"",$C27/$B27)</f>
         <v/>
       </c>
@@ -7050,23 +7052,23 @@
       <c r="O27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="45" t="str">
+      <c r="A28" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A31="","",'Budget Setup'!A31)</f>
         <v/>
       </c>
-      <c r="B28" s="46" t="str">
+      <c r="B28" s="47" t="str">
         <f aca="false">IF($A28="","",'Budget Setup'!B31)</f>
         <v/>
       </c>
-      <c r="C28" s="46" t="str">
+      <c r="C28" s="47" t="str">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v/>
       </c>
-      <c r="D28" s="46" t="str">
+      <c r="D28" s="47" t="str">
         <f aca="false">IF($A28="","",$B28-$C28)</f>
         <v/>
       </c>
-      <c r="E28" s="47" t="str">
+      <c r="E28" s="48" t="str">
         <f aca="false">IF(OR($A28="",$B28=0),"",$C28/$B28)</f>
         <v/>
       </c>
@@ -7082,23 +7084,23 @@
       <c r="O28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="45" t="str">
+      <c r="A29" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A32="","",'Budget Setup'!A32)</f>
         <v/>
       </c>
-      <c r="B29" s="46" t="str">
+      <c r="B29" s="47" t="str">
         <f aca="false">IF($A29="","",'Budget Setup'!B32)</f>
         <v/>
       </c>
-      <c r="C29" s="46" t="str">
+      <c r="C29" s="47" t="str">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v/>
       </c>
-      <c r="D29" s="46" t="str">
+      <c r="D29" s="47" t="str">
         <f aca="false">IF($A29="","",$B29-$C29)</f>
         <v/>
       </c>
-      <c r="E29" s="47" t="str">
+      <c r="E29" s="48" t="str">
         <f aca="false">IF(OR($A29="",$B29=0),"",$C29/$B29)</f>
         <v/>
       </c>
@@ -7114,23 +7116,23 @@
       <c r="O29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="45" t="str">
+      <c r="A30" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A33="","",'Budget Setup'!A33)</f>
         <v/>
       </c>
-      <c r="B30" s="46" t="str">
+      <c r="B30" s="47" t="str">
         <f aca="false">IF($A30="","",'Budget Setup'!B33)</f>
         <v/>
       </c>
-      <c r="C30" s="46" t="str">
+      <c r="C30" s="47" t="str">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v/>
       </c>
-      <c r="D30" s="46" t="str">
+      <c r="D30" s="47" t="str">
         <f aca="false">IF($A30="","",$B30-$C30)</f>
         <v/>
       </c>
-      <c r="E30" s="47" t="str">
+      <c r="E30" s="48" t="str">
         <f aca="false">IF(OR($A30="",$B30=0),"",$C30/$B30)</f>
         <v/>
       </c>
@@ -7146,23 +7148,23 @@
       <c r="O30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="45" t="str">
+      <c r="A31" s="46" t="str">
         <f aca="false">IF('Budget Setup'!A34="","",'Budget Setup'!A34)</f>
         <v/>
       </c>
-      <c r="B31" s="46" t="str">
+      <c r="B31" s="47" t="str">
         <f aca="false">IF($A31="","",'Budget Setup'!B34)</f>
         <v/>
       </c>
-      <c r="C31" s="46" t="str">
+      <c r="C31" s="47" t="str">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)))</f>
         <v/>
       </c>
-      <c r="D31" s="46" t="str">
+      <c r="D31" s="47" t="str">
         <f aca="false">IF($A31="","",$B31-$C31)</f>
         <v/>
       </c>
-      <c r="E31" s="47" t="str">
+      <c r="E31" s="48" t="str">
         <f aca="false">IF(OR($A31="",$B31=0),"",$C31/$B31)</f>
         <v/>
       </c>
@@ -7195,13 +7197,13 @@
       <c r="O32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="48" t="s">
+      <c r="A33" s="49" t="s">
         <v>112</v>
       </c>
-      <c r="B33" s="49"/>
-      <c r="C33" s="49"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -7214,14 +7216,14 @@
       <c r="O33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="50" t="str">
+      <c r="A34" s="51" t="str">
         <f aca="true">IFERROR(IF($E$7=0,"No spending logged for this month yet.",IF(AND($B$4=MONTH(TODAY()),$D$4=YEAR(TODAY())),"On pace for "&amp;TEXT(ROUND($E$7/DAY(TODAY())*DAY(EOMONTH(TODAY(),0)),0),"$#,##0")&amp;" by month-end — "&amp;IF(ROUND($E$7/DAY(TODAY())*DAY(EOMONTH(TODAY(),0)),0)&lt;=$C$7,"under","over")&amp;" your "&amp;TEXT($C$7,"$#,##0")&amp;" budget.","You spent "&amp;TEXT($E$7,"$#,##0")&amp;" — "&amp;TEXT($E$7/$C$7,"0%")&amp;" of budget.")),"")</f>
         <v>On pace for $4,607 by month-end — over your $4,455 budget.</v>
       </c>
-      <c r="B34" s="50"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -7234,14 +7236,14 @@
       <c r="O34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="50" t="str">
+      <c r="A35" s="51" t="str">
         <f aca="false">IFERROR(IF(MIN($D$12:$D$31)&lt;0,INDEX($A$12:$A$31,MATCH(MIN($D$12:$D$31),$D$12:$D$31,0))&amp;" is "&amp;TEXT(-MIN($D$12:$D$31),"$#,##0")&amp;" over budget — your biggest overrun.","No category is over budget."),"")</f>
         <v>No category is over budget.</v>
       </c>
-      <c r="B35" s="50"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -7254,14 +7256,14 @@
       <c r="O35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="50" t="str">
+      <c r="A36" s="51" t="str">
         <f aca="false">IFERROR(IF(MAX($D$12:$D$31)&gt;0,"Most room left: "&amp;INDEX($A$12:$A$31,MATCH(MAX($D$12:$D$31),$D$12:$D$31,0))&amp;" ("&amp;TEXT(MAX($D$12:$D$31),"$#,##0")&amp;" unspent).",""),"")</f>
         <v>Most room left: Savings &amp; investing ($500 unspent).</v>
       </c>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -7274,14 +7276,14 @@
       <c r="O36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="50" t="str">
+      <c r="A37" s="51" t="str">
         <f aca="false">IFERROR(IF(SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4,1))=0,"Nothing was logged the month before.",IF($E$7&gt;=SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4,1)),"▲ Spending is up ","▼ Spending is down ")&amp;TEXT(ABS($E$7-SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4,1)))/SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4,1)),"0%")&amp;" vs the month before."),"")</f>
         <v>▼ Spending is down 5% vs the month before.</v>
       </c>
-      <c r="B37" s="50"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -7294,14 +7296,14 @@
       <c r="O37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="50" t="str">
+      <c r="A38" s="51" t="str">
         <f aca="false">IFERROR(IF($E$7=0,"","Largest single purchase this month: "&amp;TEXT(_xlfn.MAXIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($D$4,$B$4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($D$4,$B$4+1,1)),"$#,##0")&amp;"."),"")</f>
         <v>Largest single purchase this month: $1,600.</v>
       </c>
-      <c r="B38" s="50"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -7453,10 +7455,10 @@
     <mergeCell ref="A38:E38"/>
   </mergeCells>
   <conditionalFormatting sqref="E12:E31">
-    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0.8</formula>
     </cfRule>
     <cfRule type="dataBar" priority="4">
@@ -7467,7 +7469,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{89AFAB4C-2C1F-4586-B865-2488F013F010}</x14:id>
+          <x14:id>{A7F1381C-EBD4-44F0-868C-C6D560D36B4B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7490,7 +7492,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{89AFAB4C-2C1F-4586-B865-2488F013F010}">
+          <x14:cfRule type="dataBar" id="{A7F1381C-EBD4-44F0-868C-C6D560D36B4B}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -7642,7 +7644,7 @@
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
         <v>116</v>
       </c>
@@ -7667,14 +7669,14 @@
       <c r="P7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="46" t="n">
+      <c r="B8" s="47" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,2,1))</f>
         <v>0</v>
       </c>
-      <c r="C8" s="47" t="n">
+      <c r="C8" s="48" t="n">
         <f aca="false">IF('Budget Setup'!$B$36=0,"",$B8/'Budget Setup'!$B$36)</f>
         <v>0</v>
       </c>
@@ -7693,14 +7695,14 @@
       <c r="P8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="46" t="n">
+      <c r="B9" s="47" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,2,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,3,1))</f>
         <v>0</v>
       </c>
-      <c r="C9" s="47" t="n">
+      <c r="C9" s="48" t="n">
         <f aca="false">IF('Budget Setup'!$B$36=0,"",$B9/'Budget Setup'!$B$36)</f>
         <v>0</v>
       </c>
@@ -7719,14 +7721,14 @@
       <c r="P9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="46" t="n">
+      <c r="B10" s="47" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,3,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,4,1))</f>
         <v>0</v>
       </c>
-      <c r="C10" s="47" t="n">
+      <c r="C10" s="48" t="n">
         <f aca="false">IF('Budget Setup'!$B$36=0,"",$B10/'Budget Setup'!$B$36)</f>
         <v>0</v>
       </c>
@@ -7745,14 +7747,14 @@
       <c r="P10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="46" t="n">
+      <c r="B11" s="47" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,4,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,5,1))</f>
         <v>0</v>
       </c>
-      <c r="C11" s="47" t="n">
+      <c r="C11" s="48" t="n">
         <f aca="false">IF('Budget Setup'!$B$36=0,"",$B11/'Budget Setup'!$B$36)</f>
         <v>0</v>
       </c>
@@ -7771,14 +7773,14 @@
       <c r="P11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="46" t="n">
+      <c r="B12" s="47" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,5,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,6,1))</f>
         <v>0</v>
       </c>
-      <c r="C12" s="47" t="n">
+      <c r="C12" s="48" t="n">
         <f aca="false">IF('Budget Setup'!$B$36=0,"",$B12/'Budget Setup'!$B$36)</f>
         <v>0</v>
       </c>
@@ -7797,14 +7799,14 @@
       <c r="P12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="B13" s="46" t="n">
+      <c r="B13" s="47" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,6,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,7,1))</f>
         <v>0</v>
       </c>
-      <c r="C13" s="47" t="n">
+      <c r="C13" s="48" t="n">
         <f aca="false">IF('Budget Setup'!$B$36=0,"",$B13/'Budget Setup'!$B$36)</f>
         <v>0</v>
       </c>
@@ -7823,14 +7825,14 @@
       <c r="P13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="B14" s="46" t="n">
+      <c r="B14" s="47" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,7,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,8,1))</f>
         <v>1873.5</v>
       </c>
-      <c r="C14" s="47" t="n">
+      <c r="C14" s="48" t="n">
         <f aca="false">IF('Budget Setup'!$B$36=0,"",$B14/'Budget Setup'!$B$36)</f>
         <v>0.420538720538721</v>
       </c>
@@ -7849,14 +7851,14 @@
       <c r="P14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="B15" s="46" t="n">
+      <c r="B15" s="47" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,8,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,9,1))</f>
         <v>1783.5</v>
       </c>
-      <c r="C15" s="47" t="n">
+      <c r="C15" s="48" t="n">
         <f aca="false">IF('Budget Setup'!$B$36=0,"",$B15/'Budget Setup'!$B$36)</f>
         <v>0.4003367003367</v>
       </c>
@@ -7875,14 +7877,14 @@
       <c r="P15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="B16" s="46" t="n">
+      <c r="B16" s="47" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,9,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,10,1))</f>
         <v>0</v>
       </c>
-      <c r="C16" s="47" t="n">
+      <c r="C16" s="48" t="n">
         <f aca="false">IF('Budget Setup'!$B$36=0,"",$B16/'Budget Setup'!$B$36)</f>
         <v>0</v>
       </c>
@@ -7901,14 +7903,14 @@
       <c r="P16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="B17" s="46" t="n">
+      <c r="B17" s="47" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,10,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,11,1))</f>
         <v>0</v>
       </c>
-      <c r="C17" s="47" t="n">
+      <c r="C17" s="48" t="n">
         <f aca="false">IF('Budget Setup'!$B$36=0,"",$B17/'Budget Setup'!$B$36)</f>
         <v>0</v>
       </c>
@@ -7927,14 +7929,14 @@
       <c r="P17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="46" t="n">
+      <c r="B18" s="47" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,11,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,12,1))</f>
         <v>0</v>
       </c>
-      <c r="C18" s="47" t="n">
+      <c r="C18" s="48" t="n">
         <f aca="false">IF('Budget Setup'!$B$36=0,"",$B18/'Budget Setup'!$B$36)</f>
         <v>0</v>
       </c>
@@ -7953,14 +7955,14 @@
       <c r="P18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="45" t="s">
+      <c r="A19" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="B19" s="46" t="n">
+      <c r="B19" s="47" t="n">
         <f aca="false">SUMIFS(Transactions!$D$6:$D$305,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,12,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,13,1))</f>
         <v>0</v>
       </c>
-      <c r="C19" s="47" t="n">
+      <c r="C19" s="48" t="n">
         <f aca="false">IF('Budget Setup'!$B$36=0,"",$B19/'Budget Setup'!$B$36)</f>
         <v>0</v>
       </c>
@@ -7982,7 +7984,7 @@
       <c r="A20" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="B20" s="51" t="n">
+      <c r="B20" s="52" t="n">
         <f aca="false">SUM(B8:B19)</f>
         <v>3657</v>
       </c>
@@ -8077,7 +8079,7 @@
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
     </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
         <v>33</v>
       </c>
@@ -8122,55 +8124,55 @@
       <c r="P25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="52" t="str">
+      <c r="A26" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A15="","",'Budget Setup'!A15)</f>
         <v>Housing</v>
       </c>
-      <c r="B26" s="53" t="n">
+      <c r="B26" s="54" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C26" s="53" t="n">
+      <c r="C26" s="54" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D26" s="53" t="n">
+      <c r="D26" s="54" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E26" s="53" t="n">
+      <c r="E26" s="54" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F26" s="53" t="n">
+      <c r="F26" s="54" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G26" s="53" t="n">
+      <c r="G26" s="54" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H26" s="53" t="n">
+      <c r="H26" s="54" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>1600</v>
       </c>
-      <c r="I26" s="53" t="n">
+      <c r="I26" s="54" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>1600</v>
       </c>
-      <c r="J26" s="53" t="n">
+      <c r="J26" s="54" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K26" s="53" t="n">
+      <c r="K26" s="54" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L26" s="53" t="n">
+      <c r="L26" s="54" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M26" s="53" t="n">
+      <c r="M26" s="54" t="n">
         <f aca="false">IF($A26="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A26,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8179,55 +8181,55 @@
       <c r="P26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="52" t="str">
+      <c r="A27" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A16="","",'Budget Setup'!A16)</f>
         <v>Groceries</v>
       </c>
-      <c r="B27" s="53" t="n">
+      <c r="B27" s="54" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C27" s="53" t="n">
+      <c r="C27" s="54" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D27" s="53" t="n">
+      <c r="D27" s="54" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E27" s="53" t="n">
+      <c r="E27" s="54" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F27" s="53" t="n">
+      <c r="F27" s="54" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G27" s="53" t="n">
+      <c r="G27" s="54" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H27" s="53" t="n">
+      <c r="H27" s="54" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>184.5</v>
       </c>
-      <c r="I27" s="53" t="n">
+      <c r="I27" s="54" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>84.2</v>
       </c>
-      <c r="J27" s="53" t="n">
+      <c r="J27" s="54" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K27" s="53" t="n">
+      <c r="K27" s="54" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L27" s="53" t="n">
+      <c r="L27" s="54" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M27" s="53" t="n">
+      <c r="M27" s="54" t="n">
         <f aca="false">IF($A27="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A27,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8236,55 +8238,55 @@
       <c r="P27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="52" t="str">
+      <c r="A28" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A17="","",'Budget Setup'!A17)</f>
         <v>Dining out</v>
       </c>
-      <c r="B28" s="53" t="n">
+      <c r="B28" s="54" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C28" s="53" t="n">
+      <c r="C28" s="54" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D28" s="53" t="n">
+      <c r="D28" s="54" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E28" s="53" t="n">
+      <c r="E28" s="54" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F28" s="53" t="n">
+      <c r="F28" s="54" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G28" s="53" t="n">
+      <c r="G28" s="54" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H28" s="53" t="n">
+      <c r="H28" s="54" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I28" s="53" t="n">
+      <c r="I28" s="54" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>56.8</v>
       </c>
-      <c r="J28" s="53" t="n">
+      <c r="J28" s="54" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K28" s="53" t="n">
+      <c r="K28" s="54" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L28" s="53" t="n">
+      <c r="L28" s="54" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M28" s="53" t="n">
+      <c r="M28" s="54" t="n">
         <f aca="false">IF($A28="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A28,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8293,55 +8295,55 @@
       <c r="P28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="52" t="str">
+      <c r="A29" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A18="","",'Budget Setup'!A18)</f>
         <v>Transport</v>
       </c>
-      <c r="B29" s="53" t="n">
+      <c r="B29" s="54" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C29" s="53" t="n">
+      <c r="C29" s="54" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D29" s="53" t="n">
+      <c r="D29" s="54" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E29" s="53" t="n">
+      <c r="E29" s="54" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F29" s="53" t="n">
+      <c r="F29" s="54" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G29" s="53" t="n">
+      <c r="G29" s="54" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H29" s="53" t="n">
+      <c r="H29" s="54" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I29" s="53" t="n">
+      <c r="I29" s="54" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>42.5</v>
       </c>
-      <c r="J29" s="53" t="n">
+      <c r="J29" s="54" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K29" s="53" t="n">
+      <c r="K29" s="54" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L29" s="53" t="n">
+      <c r="L29" s="54" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M29" s="53" t="n">
+      <c r="M29" s="54" t="n">
         <f aca="false">IF($A29="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A29,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8350,55 +8352,55 @@
       <c r="P29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="52" t="str">
+      <c r="A30" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A19="","",'Budget Setup'!A19)</f>
         <v>Utilities</v>
       </c>
-      <c r="B30" s="53" t="n">
+      <c r="B30" s="54" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C30" s="53" t="n">
+      <c r="C30" s="54" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D30" s="53" t="n">
+      <c r="D30" s="54" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E30" s="53" t="n">
+      <c r="E30" s="54" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F30" s="53" t="n">
+      <c r="F30" s="54" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G30" s="53" t="n">
+      <c r="G30" s="54" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H30" s="53" t="n">
+      <c r="H30" s="54" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I30" s="53" t="n">
+      <c r="I30" s="54" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J30" s="53" t="n">
+      <c r="J30" s="54" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K30" s="53" t="n">
+      <c r="K30" s="54" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L30" s="53" t="n">
+      <c r="L30" s="54" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M30" s="53" t="n">
+      <c r="M30" s="54" t="n">
         <f aca="false">IF($A30="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A30,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8407,55 +8409,55 @@
       <c r="P30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="52" t="str">
+      <c r="A31" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A20="","",'Budget Setup'!A20)</f>
         <v>Phone &amp; internet</v>
       </c>
-      <c r="B31" s="53" t="n">
+      <c r="B31" s="54" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C31" s="53" t="n">
+      <c r="C31" s="54" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D31" s="53" t="n">
+      <c r="D31" s="54" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E31" s="53" t="n">
+      <c r="E31" s="54" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F31" s="53" t="n">
+      <c r="F31" s="54" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G31" s="53" t="n">
+      <c r="G31" s="54" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H31" s="53" t="n">
+      <c r="H31" s="54" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I31" s="53" t="n">
+      <c r="I31" s="54" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J31" s="53" t="n">
+      <c r="J31" s="54" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K31" s="53" t="n">
+      <c r="K31" s="54" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L31" s="53" t="n">
+      <c r="L31" s="54" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M31" s="53" t="n">
+      <c r="M31" s="54" t="n">
         <f aca="false">IF($A31="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A31,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8464,55 +8466,55 @@
       <c r="P31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="52" t="str">
+      <c r="A32" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A21="","",'Budget Setup'!A21)</f>
         <v>Insurance</v>
       </c>
-      <c r="B32" s="53" t="n">
+      <c r="B32" s="54" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C32" s="53" t="n">
+      <c r="C32" s="54" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D32" s="53" t="n">
+      <c r="D32" s="54" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E32" s="53" t="n">
+      <c r="E32" s="54" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F32" s="53" t="n">
+      <c r="F32" s="54" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G32" s="53" t="n">
+      <c r="G32" s="54" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H32" s="53" t="n">
+      <c r="H32" s="54" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I32" s="53" t="n">
+      <c r="I32" s="54" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J32" s="53" t="n">
+      <c r="J32" s="54" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K32" s="53" t="n">
+      <c r="K32" s="54" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L32" s="53" t="n">
+      <c r="L32" s="54" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M32" s="53" t="n">
+      <c r="M32" s="54" t="n">
         <f aca="false">IF($A32="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A32,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8521,55 +8523,55 @@
       <c r="P32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="52" t="str">
+      <c r="A33" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A22="","",'Budget Setup'!A22)</f>
         <v>Health &amp; fitness</v>
       </c>
-      <c r="B33" s="53" t="n">
+      <c r="B33" s="54" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C33" s="53" t="n">
+      <c r="C33" s="54" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D33" s="53" t="n">
+      <c r="D33" s="54" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E33" s="53" t="n">
+      <c r="E33" s="54" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F33" s="53" t="n">
+      <c r="F33" s="54" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G33" s="53" t="n">
+      <c r="G33" s="54" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H33" s="53" t="n">
+      <c r="H33" s="54" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I33" s="53" t="n">
+      <c r="I33" s="54" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J33" s="53" t="n">
+      <c r="J33" s="54" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K33" s="53" t="n">
+      <c r="K33" s="54" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L33" s="53" t="n">
+      <c r="L33" s="54" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M33" s="53" t="n">
+      <c r="M33" s="54" t="n">
         <f aca="false">IF($A33="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A33,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8578,55 +8580,55 @@
       <c r="P33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="52" t="str">
+      <c r="A34" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A23="","",'Budget Setup'!A23)</f>
         <v>Entertainment</v>
       </c>
-      <c r="B34" s="53" t="n">
+      <c r="B34" s="54" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C34" s="53" t="n">
+      <c r="C34" s="54" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D34" s="53" t="n">
+      <c r="D34" s="54" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E34" s="53" t="n">
+      <c r="E34" s="54" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F34" s="53" t="n">
+      <c r="F34" s="54" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G34" s="53" t="n">
+      <c r="G34" s="54" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H34" s="53" t="n">
+      <c r="H34" s="54" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>89</v>
       </c>
-      <c r="I34" s="53" t="n">
+      <c r="I34" s="54" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J34" s="53" t="n">
+      <c r="J34" s="54" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K34" s="53" t="n">
+      <c r="K34" s="54" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L34" s="53" t="n">
+      <c r="L34" s="54" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M34" s="53" t="n">
+      <c r="M34" s="54" t="n">
         <f aca="false">IF($A34="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A34,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8635,55 +8637,55 @@
       <c r="P34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="52" t="str">
+      <c r="A35" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A24="","",'Budget Setup'!A24)</f>
         <v>Subscriptions</v>
       </c>
-      <c r="B35" s="53" t="n">
+      <c r="B35" s="54" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C35" s="53" t="n">
+      <c r="C35" s="54" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D35" s="53" t="n">
+      <c r="D35" s="54" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E35" s="53" t="n">
+      <c r="E35" s="54" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F35" s="53" t="n">
+      <c r="F35" s="54" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G35" s="53" t="n">
+      <c r="G35" s="54" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H35" s="53" t="n">
+      <c r="H35" s="54" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I35" s="53" t="n">
+      <c r="I35" s="54" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J35" s="53" t="n">
+      <c r="J35" s="54" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K35" s="53" t="n">
+      <c r="K35" s="54" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L35" s="53" t="n">
+      <c r="L35" s="54" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M35" s="53" t="n">
+      <c r="M35" s="54" t="n">
         <f aca="false">IF($A35="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A35,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8692,55 +8694,55 @@
       <c r="P35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="52" t="str">
+      <c r="A36" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A25="","",'Budget Setup'!A25)</f>
         <v>Shopping</v>
       </c>
-      <c r="B36" s="53" t="n">
+      <c r="B36" s="54" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C36" s="53" t="n">
+      <c r="C36" s="54" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D36" s="53" t="n">
+      <c r="D36" s="54" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E36" s="53" t="n">
+      <c r="E36" s="54" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F36" s="53" t="n">
+      <c r="F36" s="54" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G36" s="53" t="n">
+      <c r="G36" s="54" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H36" s="53" t="n">
+      <c r="H36" s="54" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I36" s="53" t="n">
+      <c r="I36" s="54" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J36" s="53" t="n">
+      <c r="J36" s="54" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K36" s="53" t="n">
+      <c r="K36" s="54" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L36" s="53" t="n">
+      <c r="L36" s="54" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M36" s="53" t="n">
+      <c r="M36" s="54" t="n">
         <f aca="false">IF($A36="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A36,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8749,55 +8751,55 @@
       <c r="P36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="52" t="str">
+      <c r="A37" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A26="","",'Budget Setup'!A26)</f>
         <v>Personal care</v>
       </c>
-      <c r="B37" s="53" t="n">
+      <c r="B37" s="54" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C37" s="53" t="n">
+      <c r="C37" s="54" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D37" s="53" t="n">
+      <c r="D37" s="54" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E37" s="53" t="n">
+      <c r="E37" s="54" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F37" s="53" t="n">
+      <c r="F37" s="54" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G37" s="53" t="n">
+      <c r="G37" s="54" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H37" s="53" t="n">
+      <c r="H37" s="54" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I37" s="53" t="n">
+      <c r="I37" s="54" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J37" s="53" t="n">
+      <c r="J37" s="54" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K37" s="53" t="n">
+      <c r="K37" s="54" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L37" s="53" t="n">
+      <c r="L37" s="54" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M37" s="53" t="n">
+      <c r="M37" s="54" t="n">
         <f aca="false">IF($A37="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A37,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8806,55 +8808,55 @@
       <c r="P37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="52" t="str">
+      <c r="A38" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A27="","",'Budget Setup'!A27)</f>
         <v>Savings &amp; investing</v>
       </c>
-      <c r="B38" s="53" t="n">
+      <c r="B38" s="54" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C38" s="53" t="n">
+      <c r="C38" s="54" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D38" s="53" t="n">
+      <c r="D38" s="54" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E38" s="53" t="n">
+      <c r="E38" s="54" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F38" s="53" t="n">
+      <c r="F38" s="54" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G38" s="53" t="n">
+      <c r="G38" s="54" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H38" s="53" t="n">
+      <c r="H38" s="54" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I38" s="53" t="n">
+      <c r="I38" s="54" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J38" s="53" t="n">
+      <c r="J38" s="54" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K38" s="53" t="n">
+      <c r="K38" s="54" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L38" s="53" t="n">
+      <c r="L38" s="54" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M38" s="53" t="n">
+      <c r="M38" s="54" t="n">
         <f aca="false">IF($A38="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A38,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8863,55 +8865,55 @@
       <c r="P38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="52" t="str">
+      <c r="A39" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A28="","",'Budget Setup'!A28)</f>
         <v>Debt payments</v>
       </c>
-      <c r="B39" s="53" t="n">
+      <c r="B39" s="54" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C39" s="53" t="n">
+      <c r="C39" s="54" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D39" s="53" t="n">
+      <c r="D39" s="54" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E39" s="53" t="n">
+      <c r="E39" s="54" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F39" s="53" t="n">
+      <c r="F39" s="54" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G39" s="53" t="n">
+      <c r="G39" s="54" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H39" s="53" t="n">
+      <c r="H39" s="54" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I39" s="53" t="n">
+      <c r="I39" s="54" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J39" s="53" t="n">
+      <c r="J39" s="54" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K39" s="53" t="n">
+      <c r="K39" s="54" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L39" s="53" t="n">
+      <c r="L39" s="54" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M39" s="53" t="n">
+      <c r="M39" s="54" t="n">
         <f aca="false">IF($A39="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A39,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8920,55 +8922,55 @@
       <c r="P39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="52" t="str">
+      <c r="A40" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A29="","",'Budget Setup'!A29)</f>
         <v>Everything else</v>
       </c>
-      <c r="B40" s="53" t="n">
+      <c r="B40" s="54" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="C40" s="53" t="n">
+      <c r="C40" s="54" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="D40" s="53" t="n">
+      <c r="D40" s="54" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="E40" s="53" t="n">
+      <c r="E40" s="54" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="F40" s="53" t="n">
+      <c r="F40" s="54" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="G40" s="53" t="n">
+      <c r="G40" s="54" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="H40" s="53" t="n">
+      <c r="H40" s="54" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="I40" s="53" t="n">
+      <c r="I40" s="54" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="J40" s="53" t="n">
+      <c r="J40" s="54" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="K40" s="53" t="n">
+      <c r="K40" s="54" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="L40" s="53" t="n">
+      <c r="L40" s="54" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
-      <c r="M40" s="53" t="n">
+      <c r="M40" s="54" t="n">
         <f aca="false">IF($A40="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A40,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v>0</v>
       </c>
@@ -8977,55 +8979,55 @@
       <c r="P40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="52" t="str">
+      <c r="A41" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A30="","",'Budget Setup'!A30)</f>
         <v/>
       </c>
-      <c r="B41" s="53" t="str">
+      <c r="B41" s="54" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="C41" s="53" t="str">
+      <c r="C41" s="54" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="D41" s="53" t="str">
+      <c r="D41" s="54" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="E41" s="53" t="str">
+      <c r="E41" s="54" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="F41" s="53" t="str">
+      <c r="F41" s="54" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="G41" s="53" t="str">
+      <c r="G41" s="54" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="H41" s="53" t="str">
+      <c r="H41" s="54" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="I41" s="53" t="str">
+      <c r="I41" s="54" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="J41" s="53" t="str">
+      <c r="J41" s="54" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="K41" s="53" t="str">
+      <c r="K41" s="54" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="L41" s="53" t="str">
+      <c r="L41" s="54" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="M41" s="53" t="str">
+      <c r="M41" s="54" t="str">
         <f aca="false">IF($A41="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A41,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
@@ -9034,55 +9036,55 @@
       <c r="P41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="52" t="str">
+      <c r="A42" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A31="","",'Budget Setup'!A31)</f>
         <v/>
       </c>
-      <c r="B42" s="53" t="str">
+      <c r="B42" s="54" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="C42" s="53" t="str">
+      <c r="C42" s="54" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="D42" s="53" t="str">
+      <c r="D42" s="54" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="E42" s="53" t="str">
+      <c r="E42" s="54" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="F42" s="53" t="str">
+      <c r="F42" s="54" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="G42" s="53" t="str">
+      <c r="G42" s="54" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="H42" s="53" t="str">
+      <c r="H42" s="54" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="I42" s="53" t="str">
+      <c r="I42" s="54" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="J42" s="53" t="str">
+      <c r="J42" s="54" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="K42" s="53" t="str">
+      <c r="K42" s="54" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="L42" s="53" t="str">
+      <c r="L42" s="54" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="M42" s="53" t="str">
+      <c r="M42" s="54" t="str">
         <f aca="false">IF($A42="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A42,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
@@ -9091,55 +9093,55 @@
       <c r="P42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="52" t="str">
+      <c r="A43" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A32="","",'Budget Setup'!A32)</f>
         <v/>
       </c>
-      <c r="B43" s="53" t="str">
+      <c r="B43" s="54" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="C43" s="53" t="str">
+      <c r="C43" s="54" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="D43" s="53" t="str">
+      <c r="D43" s="54" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="E43" s="53" t="str">
+      <c r="E43" s="54" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="F43" s="53" t="str">
+      <c r="F43" s="54" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="G43" s="53" t="str">
+      <c r="G43" s="54" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="H43" s="53" t="str">
+      <c r="H43" s="54" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="I43" s="53" t="str">
+      <c r="I43" s="54" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="J43" s="53" t="str">
+      <c r="J43" s="54" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="K43" s="53" t="str">
+      <c r="K43" s="54" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="L43" s="53" t="str">
+      <c r="L43" s="54" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="M43" s="53" t="str">
+      <c r="M43" s="54" t="str">
         <f aca="false">IF($A43="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A43,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
@@ -9148,55 +9150,55 @@
       <c r="P43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="52" t="str">
+      <c r="A44" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A33="","",'Budget Setup'!A33)</f>
         <v/>
       </c>
-      <c r="B44" s="53" t="str">
+      <c r="B44" s="54" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="C44" s="53" t="str">
+      <c r="C44" s="54" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="D44" s="53" t="str">
+      <c r="D44" s="54" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="E44" s="53" t="str">
+      <c r="E44" s="54" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="F44" s="53" t="str">
+      <c r="F44" s="54" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="G44" s="53" t="str">
+      <c r="G44" s="54" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="H44" s="53" t="str">
+      <c r="H44" s="54" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="I44" s="53" t="str">
+      <c r="I44" s="54" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="J44" s="53" t="str">
+      <c r="J44" s="54" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="K44" s="53" t="str">
+      <c r="K44" s="54" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="L44" s="53" t="str">
+      <c r="L44" s="54" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="M44" s="53" t="str">
+      <c r="M44" s="54" t="str">
         <f aca="false">IF($A44="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A44,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
@@ -9205,55 +9207,55 @@
       <c r="P44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="52" t="str">
+      <c r="A45" s="53" t="str">
         <f aca="false">IF('Budget Setup'!A34="","",'Budget Setup'!A34)</f>
         <v/>
       </c>
-      <c r="B45" s="53" t="str">
+      <c r="B45" s="54" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="C45" s="53" t="str">
+      <c r="C45" s="54" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="D45" s="53" t="str">
+      <c r="D45" s="54" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="E45" s="53" t="str">
+      <c r="E45" s="54" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="F45" s="53" t="str">
+      <c r="F45" s="54" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="G45" s="53" t="str">
+      <c r="G45" s="54" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="H45" s="53" t="str">
+      <c r="H45" s="54" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="I45" s="53" t="str">
+      <c r="I45" s="54" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="J45" s="53" t="str">
+      <c r="J45" s="54" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="K45" s="53" t="str">
+      <c r="K45" s="54" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="L45" s="53" t="str">
+      <c r="L45" s="54" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
-      <c r="M45" s="53" t="str">
+      <c r="M45" s="54" t="str">
         <f aca="false">IF($A45="","",SUMIFS(Transactions!$D$6:$D$305,Transactions!$C$6:$C$305,$A45,Transactions!$A$6:$A$305,"&gt;="&amp;DATE($B$4,COLUMN()-1,1),Transactions!$A$6:$A$305,"&lt;"&amp;DATE($B$4,COLUMN(),1)))</f>
         <v/>
       </c>
@@ -9410,7 +9412,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
         <v>136</v>
       </c>
@@ -9445,18 +9447,18 @@
       <c r="C6" s="14" t="n">
         <v>1150</v>
       </c>
-      <c r="D6" s="54" t="n">
+      <c r="D6" s="55" t="n">
         <v>46387</v>
       </c>
-      <c r="E6" s="55" t="n">
+      <c r="E6" s="56" t="n">
         <f aca="true">IF(OR($A6="",$D6=""),"",MAX(0,(YEAR($D6)-YEAR(TODAY()))*12+MONTH($D6)-MONTH(TODAY())))</f>
         <v>4</v>
       </c>
-      <c r="F6" s="56" t="n">
+      <c r="F6" s="57" t="n">
         <f aca="false">IF(OR($A6="",$B6="",$D6=""),"",IF($E6=0,MAX(0,$B6-$C6),ROUND(MAX(0,$B6-$C6)/$E6,2)))</f>
         <v>462.5</v>
       </c>
-      <c r="G6" s="47" t="n">
+      <c r="G6" s="48" t="n">
         <f aca="false">IF(OR($A6="",$B6="",$B6=0),"",MIN(1,$C6/$B6))</f>
         <v>0.383333333333333</v>
       </c>
@@ -9473,18 +9475,18 @@
       <c r="C7" s="14" t="n">
         <v>600</v>
       </c>
-      <c r="D7" s="54" t="n">
+      <c r="D7" s="55" t="n">
         <v>46568</v>
       </c>
-      <c r="E7" s="55" t="n">
+      <c r="E7" s="56" t="n">
         <f aca="true">IF(OR($A7="",$D7=""),"",MAX(0,(YEAR($D7)-YEAR(TODAY()))*12+MONTH($D7)-MONTH(TODAY())))</f>
         <v>10</v>
       </c>
-      <c r="F7" s="56" t="n">
+      <c r="F7" s="57" t="n">
         <f aca="false">IF(OR($A7="",$B7="",$D7=""),"",IF($E7=0,MAX(0,$B7-$C7),ROUND(MAX(0,$B7-$C7)/$E7,2)))</f>
         <v>180</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="48" t="n">
         <f aca="false">IF(OR($A7="",$B7="",$B7=0),"",MIN(1,$C7/$B7))</f>
         <v>0.25</v>
       </c>
@@ -9495,16 +9497,16 @@
       <c r="A8" s="13"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="55" t="str">
+      <c r="D8" s="55"/>
+      <c r="E8" s="56" t="str">
         <f aca="true">IF(OR($A8="",$D8=""),"",MAX(0,(YEAR($D8)-YEAR(TODAY()))*12+MONTH($D8)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F8" s="56" t="str">
+      <c r="F8" s="57" t="str">
         <f aca="false">IF(OR($A8="",$B8="",$D8=""),"",IF($E8=0,MAX(0,$B8-$C8),ROUND(MAX(0,$B8-$C8)/$E8,2)))</f>
         <v/>
       </c>
-      <c r="G8" s="47" t="str">
+      <c r="G8" s="48" t="str">
         <f aca="false">IF(OR($A8="",$B8="",$B8=0),"",MIN(1,$C8/$B8))</f>
         <v/>
       </c>
@@ -9515,16 +9517,16 @@
       <c r="A9" s="13"/>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="55" t="str">
+      <c r="D9" s="55"/>
+      <c r="E9" s="56" t="str">
         <f aca="true">IF(OR($A9="",$D9=""),"",MAX(0,(YEAR($D9)-YEAR(TODAY()))*12+MONTH($D9)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F9" s="56" t="str">
+      <c r="F9" s="57" t="str">
         <f aca="false">IF(OR($A9="",$B9="",$D9=""),"",IF($E9=0,MAX(0,$B9-$C9),ROUND(MAX(0,$B9-$C9)/$E9,2)))</f>
         <v/>
       </c>
-      <c r="G9" s="47" t="str">
+      <c r="G9" s="48" t="str">
         <f aca="false">IF(OR($A9="",$B9="",$B9=0),"",MIN(1,$C9/$B9))</f>
         <v/>
       </c>
@@ -9535,16 +9537,16 @@
       <c r="A10" s="13"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="55" t="str">
+      <c r="D10" s="55"/>
+      <c r="E10" s="56" t="str">
         <f aca="true">IF(OR($A10="",$D10=""),"",MAX(0,(YEAR($D10)-YEAR(TODAY()))*12+MONTH($D10)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F10" s="56" t="str">
+      <c r="F10" s="57" t="str">
         <f aca="false">IF(OR($A10="",$B10="",$D10=""),"",IF($E10=0,MAX(0,$B10-$C10),ROUND(MAX(0,$B10-$C10)/$E10,2)))</f>
         <v/>
       </c>
-      <c r="G10" s="47" t="str">
+      <c r="G10" s="48" t="str">
         <f aca="false">IF(OR($A10="",$B10="",$B10=0),"",MIN(1,$C10/$B10))</f>
         <v/>
       </c>
@@ -9555,16 +9557,16 @@
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="55" t="str">
+      <c r="D11" s="55"/>
+      <c r="E11" s="56" t="str">
         <f aca="true">IF(OR($A11="",$D11=""),"",MAX(0,(YEAR($D11)-YEAR(TODAY()))*12+MONTH($D11)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F11" s="56" t="str">
+      <c r="F11" s="57" t="str">
         <f aca="false">IF(OR($A11="",$B11="",$D11=""),"",IF($E11=0,MAX(0,$B11-$C11),ROUND(MAX(0,$B11-$C11)/$E11,2)))</f>
         <v/>
       </c>
-      <c r="G11" s="47" t="str">
+      <c r="G11" s="48" t="str">
         <f aca="false">IF(OR($A11="",$B11="",$B11=0),"",MIN(1,$C11/$B11))</f>
         <v/>
       </c>
@@ -9575,16 +9577,16 @@
       <c r="A12" s="13"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="55" t="str">
+      <c r="D12" s="55"/>
+      <c r="E12" s="56" t="str">
         <f aca="true">IF(OR($A12="",$D12=""),"",MAX(0,(YEAR($D12)-YEAR(TODAY()))*12+MONTH($D12)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F12" s="56" t="str">
+      <c r="F12" s="57" t="str">
         <f aca="false">IF(OR($A12="",$B12="",$D12=""),"",IF($E12=0,MAX(0,$B12-$C12),ROUND(MAX(0,$B12-$C12)/$E12,2)))</f>
         <v/>
       </c>
-      <c r="G12" s="47" t="str">
+      <c r="G12" s="48" t="str">
         <f aca="false">IF(OR($A12="",$B12="",$B12=0),"",MIN(1,$C12/$B12))</f>
         <v/>
       </c>
@@ -9595,16 +9597,16 @@
       <c r="A13" s="13"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="55" t="str">
+      <c r="D13" s="55"/>
+      <c r="E13" s="56" t="str">
         <f aca="true">IF(OR($A13="",$D13=""),"",MAX(0,(YEAR($D13)-YEAR(TODAY()))*12+MONTH($D13)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F13" s="56" t="str">
+      <c r="F13" s="57" t="str">
         <f aca="false">IF(OR($A13="",$B13="",$D13=""),"",IF($E13=0,MAX(0,$B13-$C13),ROUND(MAX(0,$B13-$C13)/$E13,2)))</f>
         <v/>
       </c>
-      <c r="G13" s="47" t="str">
+      <c r="G13" s="48" t="str">
         <f aca="false">IF(OR($A13="",$B13="",$B13=0),"",MIN(1,$C13/$B13))</f>
         <v/>
       </c>
@@ -9615,16 +9617,16 @@
       <c r="A14" s="13"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="55" t="str">
+      <c r="D14" s="55"/>
+      <c r="E14" s="56" t="str">
         <f aca="true">IF(OR($A14="",$D14=""),"",MAX(0,(YEAR($D14)-YEAR(TODAY()))*12+MONTH($D14)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F14" s="56" t="str">
+      <c r="F14" s="57" t="str">
         <f aca="false">IF(OR($A14="",$B14="",$D14=""),"",IF($E14=0,MAX(0,$B14-$C14),ROUND(MAX(0,$B14-$C14)/$E14,2)))</f>
         <v/>
       </c>
-      <c r="G14" s="47" t="str">
+      <c r="G14" s="48" t="str">
         <f aca="false">IF(OR($A14="",$B14="",$B14=0),"",MIN(1,$C14/$B14))</f>
         <v/>
       </c>
@@ -9635,16 +9637,16 @@
       <c r="A15" s="13"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="55" t="str">
+      <c r="D15" s="55"/>
+      <c r="E15" s="56" t="str">
         <f aca="true">IF(OR($A15="",$D15=""),"",MAX(0,(YEAR($D15)-YEAR(TODAY()))*12+MONTH($D15)-MONTH(TODAY())))</f>
         <v/>
       </c>
-      <c r="F15" s="56" t="str">
+      <c r="F15" s="57" t="str">
         <f aca="false">IF(OR($A15="",$B15="",$D15=""),"",IF($E15=0,MAX(0,$B15-$C15),ROUND(MAX(0,$B15-$C15)/$E15,2)))</f>
         <v/>
       </c>
-      <c r="G15" s="47" t="str">
+      <c r="G15" s="48" t="str">
         <f aca="false">IF(OR($A15="",$B15="",$B15=0),"",MIN(1,$C15/$B15))</f>
         <v/>
       </c>
@@ -9753,7 +9755,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F3714075-C9CA-4A22-8196-3EED44736965}</x14:id>
+          <x14:id>{004F6D6C-C58A-4367-9822-B5FE1C7643EE}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -9769,7 +9771,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F3714075-C9CA-4A22-8196-3EED44736965}">
+          <x14:cfRule type="dataBar" id="{004F6D6C-C58A-4367-9822-B5FE1C7643EE}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
